--- a/Datacenter_Infrastructure_Model.xlsx
+++ b/Datacenter_Infrastructure_Model.xlsx
@@ -19,7 +19,8 @@
     <sheet name="DC Bill of Materials" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Capex to Revenue" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Capex to AI Revenue" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Assumptions &amp; Sources" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Capex Decomposition" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Assumptions &amp; Sources" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36,7 +37,7 @@
     <numFmt numFmtId="168" formatCode="$#,##0.0"/>
     <numFmt numFmtId="169" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -110,8 +111,14 @@
       <name val="Calibri"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002E5090"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -154,6 +161,12 @@
         <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+        <bgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -181,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -396,6 +409,9 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -8852,6 +8868,909 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart50.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Component Price Indices (2020 = 100)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Capex Decomposition'!$B$6:$N$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Capex Decomposition'!$B$9:$N$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Capex Decomposition'!$B$15:$N$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Capex Decomposition'!$B$13:$N$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Capex Decomposition'!$B$7:$N$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="FF6384"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Capex Decomposition'!$B$8:$N$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart51.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Weighted-Average DC Component Index (2020 = 100)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Capex Decomposition'!$B$18:$N$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart52.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Hyperscaler Capex Decomposition ($B): Volume vs Price vs Other</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="4472C4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <val>
+            <numRef>
+              <f>'Capex Decomposition'!$B$96:$N$96</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="ED7D31"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <val>
+            <numRef>
+              <f>'Capex Decomposition'!$B$97:$N$97</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="70AD47"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <val>
+            <numRef>
+              <f>'Capex Decomposition'!$B$98:$N$98</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart53.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Capex per MW of New Capacity ($M/MW) — Hyperscalers</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Capex Decomposition'!$B$32:$N$32</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Capex Decomposition'!$B$43:$N$43</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Capex Decomposition'!$B$54:$N$54</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Capex Decomposition'!$B$65:$N$65</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Capex Decomposition'!$B$76:$N$76</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="FF6384"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Capex Decomposition'!$B$87:$N$87</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart54.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Share of Hyperscaler Capex: Volume vs Price Inflation</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="4472C4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <val>
+            <numRef>
+              <f>'Capex Decomposition'!$B$191:$N$191</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="ED7D31"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <val>
+            <numRef>
+              <f>'Capex Decomposition'!$B$190:$N$190</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart55.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Cumulative Component Inflation vs 2020 Baseline</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Capex Decomposition'!$B$23:$N$23</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
@@ -10024,6 +10943,143 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>114</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9360000" cy="5400000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>114</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="5400000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>131</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9360000" cy="5400000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>131</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="5400000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>148</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9360000" cy="5400000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>148</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="5400000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="6" name="Chart 6"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -25281,11 +26337,4280 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00BF8F00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N191"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Capex Decomposition — Capacity Growth vs Component Price Inflation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="33" t="inlineStr">
+        <is>
+          <t>How much of capex growth is real capacity addition vs component cost inflation?  |  Price index (2020=100)  |  Yellow = 2026E+ Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Component Price Indices (2020 = 100) — Unit Cost Trends by Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Component Category</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>GPU / AI Accelerators</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>130</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>170</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>250</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>310</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>280</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>240</v>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="L6" s="10" t="n">
+        <v>175</v>
+      </c>
+      <c r="M6" s="10" t="n">
+        <v>155</v>
+      </c>
+      <c r="N6" s="10" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>CPU Servers</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>105</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>96</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>94</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>88</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>86</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>84</v>
+      </c>
+      <c r="M7" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="N7" s="10" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Networking (Switches/Optics)</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>95</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>97</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>105</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>115</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>130</v>
+      </c>
+      <c r="H8" s="11" t="n">
+        <v>145</v>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>150</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>142</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>132</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>122</v>
+      </c>
+      <c r="M8" s="10" t="n">
+        <v>115</v>
+      </c>
+      <c r="N8" s="10" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>HV Transformers &amp; Switchgear</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>88</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>108</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>125</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>155</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>185</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>195</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>190</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>175</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="M9" s="10" t="n">
+        <v>148</v>
+      </c>
+      <c r="N9" s="10" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>UPS &amp; Power Distribution</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>92</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>95</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>106</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>118</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>132</v>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>145</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>150</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>148</v>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>140</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>132</v>
+      </c>
+      <c r="M10" s="10" t="n">
+        <v>125</v>
+      </c>
+      <c r="N10" s="10" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Backup Generators</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>94</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>96</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>110</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>122</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>135</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>142</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>148</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>145</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>138</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>130</v>
+      </c>
+      <c r="M11" s="10" t="n">
+        <v>125</v>
+      </c>
+      <c r="N11" s="10" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Cooling (Chillers/CRAC)</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>96</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>98</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>104</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>110</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>118</v>
+      </c>
+      <c r="H12" s="11" t="n">
+        <v>122</v>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>125</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="K12" s="10" t="n">
+        <v>115</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>110</v>
+      </c>
+      <c r="M12" s="10" t="n">
+        <v>106</v>
+      </c>
+      <c r="N12" s="10" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Liquid Cooling (DLC)</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>180</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>160</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>68</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="M13" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="N13" s="10" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Fiber &amp; Cabling</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>97</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>98</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>103</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>108</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>115</v>
+      </c>
+      <c r="H14" s="11" t="n">
+        <v>120</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>122</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>118</v>
+      </c>
+      <c r="K14" s="10" t="n">
+        <v>114</v>
+      </c>
+      <c r="L14" s="10" t="n">
+        <v>110</v>
+      </c>
+      <c r="M14" s="10" t="n">
+        <v>107</v>
+      </c>
+      <c r="N14" s="10" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Construction Labor</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>93</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>108</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>118</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>130</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>140</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>148</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>152</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="L15" s="10" t="n">
+        <v>146</v>
+      </c>
+      <c r="M15" s="10" t="n">
+        <v>142</v>
+      </c>
+      <c r="N15" s="10" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Steel &amp; Building Materials</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>88</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>92</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>130</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>142</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>128</v>
+      </c>
+      <c r="H16" s="11" t="n">
+        <v>125</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>120</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>118</v>
+      </c>
+      <c r="K16" s="10" t="n">
+        <v>115</v>
+      </c>
+      <c r="L16" s="10" t="n">
+        <v>112</v>
+      </c>
+      <c r="M16" s="10" t="n">
+        <v>110</v>
+      </c>
+      <c r="N16" s="10" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Land &amp; Real Estate</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>110</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>125</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>142</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>160</v>
+      </c>
+      <c r="I17" s="9" t="n">
+        <v>170</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>178</v>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>182</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>185</v>
+      </c>
+      <c r="M17" s="10" t="n">
+        <v>188</v>
+      </c>
+      <c r="N17" s="10" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>WEIGHTED AVG INDEX</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="C18" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="F18" s="26" t="n">
+        <v>130.7</v>
+      </c>
+      <c r="G18" s="26" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="H18" s="26" t="n">
+        <v>185</v>
+      </c>
+      <c r="I18" s="26" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="J18" s="26" t="n">
+        <v>165.1</v>
+      </c>
+      <c r="K18" s="26" t="n">
+        <v>149.6</v>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>138.4</v>
+      </c>
+      <c r="M18" s="26" t="n">
+        <v>129.4</v>
+      </c>
+      <c r="N18" s="26" t="n">
+        <v>122.4</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Weighted-Average Component Inflation (YoY % Change in Index)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Wtd-Avg Component Inflation</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>0.2195</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>0.2311</v>
+      </c>
+      <c r="H22" s="13" t="n">
+        <v>0.1498</v>
+      </c>
+      <c r="I22" s="13" t="n">
+        <v>-0.0351</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>-0.0751</v>
+      </c>
+      <c r="K22" s="14" t="n">
+        <v>-0.0939</v>
+      </c>
+      <c r="L22" s="14" t="n">
+        <v>-0.07489999999999999</v>
+      </c>
+      <c r="M22" s="14" t="n">
+        <v>-0.065</v>
+      </c>
+      <c r="N22" s="14" t="n">
+        <v>-0.0541</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Cumulative Inflation vs 2020</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>-0.189</v>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="G23" s="17" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I23" s="17" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="K23" s="14" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="L23" s="14" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="M23" s="14" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="N23" s="14" t="n">
+        <v>0.224</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Hyperscaler Capex Decomposition — Volume (New GW Added) vs Price ($/MW) vs Total Capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="33" t="inlineStr">
+        <is>
+          <t>Total Capex = New GW Added x Capex/MW  |  Volume Effect = New GW x Base $/MW (2020)  |  Price Effect = New GW x (Current $/MW - Base $/MW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="73" t="inlineStr">
+        <is>
+          <t>Amazon (AWS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Total Capex ($B)</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="C30" s="21" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="D30" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="E30" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="F30" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="G30" s="21" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="H30" s="21" t="n">
+        <v>83</v>
+      </c>
+      <c r="I30" s="21" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="J30" s="22" t="n">
+        <v>112</v>
+      </c>
+      <c r="K30" s="22" t="n">
+        <v>130</v>
+      </c>
+      <c r="L30" s="22" t="n">
+        <v>145</v>
+      </c>
+      <c r="M30" s="22" t="n">
+        <v>152</v>
+      </c>
+      <c r="N30" s="22" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>New GW Added</t>
+        </is>
+      </c>
+      <c r="B31" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D31" s="30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E31" s="30" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F31" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H31" s="30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I31" s="30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J31" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="L31" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="M31" s="29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N31" s="29" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Capex / MW Added ($M/MW)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="L32" s="7" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="N32" s="7" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Base $/MW (2020 = $8.2M)</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H33" s="12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I33" s="12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L33" s="7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="M33" s="7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="N33" s="7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Volume Effect ($B) [GW x Base $/MW]</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D34" s="21" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="E34" s="21" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="F34" s="21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G34" s="21" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="H34" s="21" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="I34" s="21" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="J34" s="22" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="K34" s="22" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="L34" s="22" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="M34" s="22" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="N34" s="22" t="n">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Price Effect ($B) [GW x Inflation $/MW]</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C35" s="23" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D35" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="23" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F35" s="23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G35" s="23" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H35" s="23" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="I35" s="23" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="J35" s="22" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="K35" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="L35" s="22" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="M35" s="22" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="N35" s="22" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Other / Maintenance ($B)</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="C36" s="21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="D36" s="21" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="E36" s="21" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="F36" s="21" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G36" s="21" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="H36" s="21" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="I36" s="21" t="n">
+        <v>63.06</v>
+      </c>
+      <c r="J36" s="22" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="K36" s="22" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="L36" s="22" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="M36" s="22" t="n">
+        <v>123.25</v>
+      </c>
+      <c r="N36" s="22" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Price Inflation % of Capacity Capex</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="17" t="n">
+        <v>-0.051</v>
+      </c>
+      <c r="D37" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="F37" s="17" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="G37" s="17" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="H37" s="17" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="I37" s="17" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="J37" s="14" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="K37" s="14" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="L37" s="14" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="M37" s="14" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="N37" s="14" t="n">
+        <v>0.268</v>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="73" t="inlineStr">
+        <is>
+          <t>Microsoft (Azure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Total Capex ($B)</t>
+        </is>
+      </c>
+      <c r="B41" s="21" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="C41" s="21" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="D41" s="21" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="E41" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="F41" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G41" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="H41" s="21" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="I41" s="21" t="n">
+        <v>88</v>
+      </c>
+      <c r="J41" s="22" t="n">
+        <v>102</v>
+      </c>
+      <c r="K41" s="22" t="n">
+        <v>115</v>
+      </c>
+      <c r="L41" s="22" t="n">
+        <v>122</v>
+      </c>
+      <c r="M41" s="22" t="n">
+        <v>126</v>
+      </c>
+      <c r="N41" s="22" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>New GW Added</t>
+        </is>
+      </c>
+      <c r="B42" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D42" s="30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E42" s="30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F42" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H42" s="30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I42" s="30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J42" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="K42" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="L42" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="M42" s="29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N42" s="29" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Capex / MW Added ($M/MW)</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I43" s="6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J43" s="7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="K43" s="7" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="L43" s="7" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="M43" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="N43" s="7" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Base $/MW (2020 = $7.8M)</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="C44" s="12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H44" s="12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I44" s="12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J44" s="7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K44" s="7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L44" s="7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M44" s="7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="N44" s="7" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Volume Effect ($B) [GW x Base $/MW]</t>
+        </is>
+      </c>
+      <c r="B45" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="21" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="D45" s="21" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="E45" s="21" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="F45" s="21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G45" s="21" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H45" s="21" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="I45" s="21" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="J45" s="22" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="K45" s="22" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="L45" s="22" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="M45" s="22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="N45" s="22" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Price Effect ($B) [GW x Inflation $/MW]</t>
+        </is>
+      </c>
+      <c r="B46" s="23" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C46" s="23" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="D46" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="23" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F46" s="23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G46" s="23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H46" s="23" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="I46" s="23" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="J46" s="22" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="K46" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="L46" s="22" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="M46" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="N46" s="22" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Other / Maintenance ($B)</t>
+        </is>
+      </c>
+      <c r="B47" s="21" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="C47" s="21" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D47" s="21" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="E47" s="21" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F47" s="21" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G47" s="21" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="H47" s="21" t="n">
+        <v>35</v>
+      </c>
+      <c r="I47" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="J47" s="22" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="K47" s="22" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="L47" s="22" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="M47" s="22" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="N47" s="22" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Price Inflation % of Capacity Capex</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="D48" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="F48" s="17" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="G48" s="17" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="H48" s="17" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="I48" s="17" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="J48" s="14" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="K48" s="14" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="L48" s="14" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="M48" s="14" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="N48" s="14" t="n">
+        <v>0.278</v>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="73" t="inlineStr">
+        <is>
+          <t>Google (GCP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="M51" s="4" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Total Capex ($B)</t>
+        </is>
+      </c>
+      <c r="B52" s="21" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="C52" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="D52" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="E52" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="F52" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G52" s="21" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="H52" s="21" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="I52" s="21" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="J52" s="22" t="n">
+        <v>86</v>
+      </c>
+      <c r="K52" s="22" t="n">
+        <v>96</v>
+      </c>
+      <c r="L52" s="22" t="n">
+        <v>102</v>
+      </c>
+      <c r="M52" s="22" t="n">
+        <v>106</v>
+      </c>
+      <c r="N52" s="22" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>New GW Added</t>
+        </is>
+      </c>
+      <c r="B53" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="30" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D53" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E53" s="30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F53" s="30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G53" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I53" s="30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J53" s="29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K53" s="29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L53" s="29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M53" s="29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N53" s="29" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Capex / MW Added ($M/MW)</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="J54" s="7" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="K54" s="7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L54" s="7" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="M54" s="7" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="N54" s="7" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>Base $/MW (2020 = $7.5M)</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C55" s="12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D55" s="12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E55" s="12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H55" s="12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I55" s="12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J55" s="7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K55" s="7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L55" s="7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M55" s="7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N55" s="7" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Volume Effect ($B) [GW x Base $/MW]</t>
+        </is>
+      </c>
+      <c r="B56" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D56" s="21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="E56" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F56" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G56" s="21" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H56" s="21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I56" s="21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J56" s="22" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="K56" s="22" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="L56" s="22" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="M56" s="22" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="N56" s="22" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>Price Effect ($B) [GW x Inflation $/MW]</t>
+        </is>
+      </c>
+      <c r="B57" s="23" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C57" s="23" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="D57" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="23" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F57" s="23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G57" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H57" s="23" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="I57" s="23" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J57" s="22" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="K57" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="L57" s="22" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="M57" s="22" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="N57" s="22" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Other / Maintenance ($B)</t>
+        </is>
+      </c>
+      <c r="B58" s="21" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="C58" s="21" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="D58" s="21" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="E58" s="21" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="F58" s="21" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G58" s="21" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="H58" s="21" t="n">
+        <v>32.34</v>
+      </c>
+      <c r="I58" s="21" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="J58" s="22" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="K58" s="22" t="n">
+        <v>67.25</v>
+      </c>
+      <c r="L58" s="22" t="n">
+        <v>74</v>
+      </c>
+      <c r="M58" s="22" t="n">
+        <v>79</v>
+      </c>
+      <c r="N58" s="22" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>Price Inflation % of Capacity Capex</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="17" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="D59" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="17" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="F59" s="17" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="G59" s="17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H59" s="17" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I59" s="17" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J59" s="14" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="K59" s="14" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="L59" s="14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M59" s="14" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="N59" s="14" t="n">
+        <v>0.286</v>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="73" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="M62" s="4" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="N62" s="4" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>Total Capex ($B)</t>
+        </is>
+      </c>
+      <c r="B63" s="21" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C63" s="21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D63" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="E63" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="F63" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="G63" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="H63" s="21" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="I63" s="21" t="n">
+        <v>62</v>
+      </c>
+      <c r="J63" s="22" t="n">
+        <v>72</v>
+      </c>
+      <c r="K63" s="22" t="n">
+        <v>78</v>
+      </c>
+      <c r="L63" s="22" t="n">
+        <v>80</v>
+      </c>
+      <c r="M63" s="22" t="n">
+        <v>81</v>
+      </c>
+      <c r="N63" s="22" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>New GW Added</t>
+        </is>
+      </c>
+      <c r="B64" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D64" s="30" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E64" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F64" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G64" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H64" s="30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I64" s="30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J64" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K64" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="L64" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="M64" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="N64" s="29" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Capex / MW Added ($M/MW)</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G65" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H65" s="6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I65" s="6" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J65" s="7" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="K65" s="7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L65" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="M65" s="7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="N65" s="7" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>Base $/MW (2020 = $8.5M)</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C66" s="12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D66" s="12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E66" s="12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F66" s="12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G66" s="12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H66" s="12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I66" s="12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J66" s="7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K66" s="7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L66" s="7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M66" s="7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="N66" s="7" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>Volume Effect ($B) [GW x Base $/MW]</t>
+        </is>
+      </c>
+      <c r="B67" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D67" s="21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E67" s="21" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F67" s="21" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="G67" s="21" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H67" s="21" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="I67" s="21" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="J67" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="K67" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="L67" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="M67" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="N67" s="22" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>Price Effect ($B) [GW x Inflation $/MW]</t>
+        </is>
+      </c>
+      <c r="B68" s="23" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C68" s="23" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="D68" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="23" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F68" s="23" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G68" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H68" s="23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I68" s="23" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="J68" s="22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K68" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="L68" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="M68" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="N68" s="22" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Other / Maintenance ($B)</t>
+        </is>
+      </c>
+      <c r="B69" s="21" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C69" s="21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D69" s="21" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="E69" s="21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F69" s="21" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G69" s="21" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H69" s="21" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="I69" s="21" t="n">
+        <v>31.64</v>
+      </c>
+      <c r="J69" s="22" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="K69" s="22" t="n">
+        <v>53</v>
+      </c>
+      <c r="L69" s="22" t="n">
+        <v>56</v>
+      </c>
+      <c r="M69" s="22" t="n">
+        <v>58</v>
+      </c>
+      <c r="N69" s="22" t="n">
+        <v>59.6</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>Price Inflation % of Capacity Capex</t>
+        </is>
+      </c>
+      <c r="B70" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="17" t="n">
+        <v>-0.063</v>
+      </c>
+      <c r="D70" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="F70" s="17" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="G70" s="17" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="H70" s="17" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I70" s="17" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="J70" s="14" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="K70" s="14" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L70" s="14" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="M70" s="14" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="N70" s="14" t="n">
+        <v>0.241</v>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="73" t="inlineStr">
+        <is>
+          <t>Oracle Cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="M73" s="4" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="N73" s="4" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Total Capex ($B)</t>
+        </is>
+      </c>
+      <c r="B74" s="21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C74" s="21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D74" s="21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E74" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F74" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G74" s="21" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H74" s="21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I74" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="J74" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="K74" s="22" t="n">
+        <v>27</v>
+      </c>
+      <c r="L74" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="M74" s="22" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="N74" s="22" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>New GW Added</t>
+        </is>
+      </c>
+      <c r="B75" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D75" s="30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E75" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F75" s="30" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G75" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H75" s="30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I75" s="30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J75" s="29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K75" s="29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L75" s="29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M75" s="29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N75" s="29" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Capex / MW Added ($M/MW)</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E76" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G76" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H76" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="I76" s="6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J76" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="K76" s="7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L76" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="M76" s="7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="N76" s="7" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>Base $/MW (2020 = $9.0M)</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C77" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="D77" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="E77" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F77" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H77" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I77" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J77" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="K77" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="L77" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="M77" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="N77" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Volume Effect ($B) [GW x Base $/MW]</t>
+        </is>
+      </c>
+      <c r="B78" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D78" s="21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E78" s="21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F78" s="21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G78" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H78" s="21" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="I78" s="21" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J78" s="22" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="K78" s="22" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="L78" s="22" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="M78" s="22" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="N78" s="22" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>Price Effect ($B) [GW x Inflation $/MW]</t>
+        </is>
+      </c>
+      <c r="B79" s="23" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C79" s="23" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F79" s="23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G79" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I79" s="23" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J79" s="22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K79" s="22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L79" s="22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M79" s="22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N79" s="22" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Other / Maintenance ($B)</t>
+        </is>
+      </c>
+      <c r="B80" s="21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C80" s="21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="D80" s="21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E80" s="21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F80" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H80" s="21" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="I80" s="21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J80" s="22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K80" s="22" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L80" s="22" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="M80" s="22" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="N80" s="22" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>Price Inflation % of Capacity Capex</t>
+        </is>
+      </c>
+      <c r="B81" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="17" t="n">
+        <v>-0.059</v>
+      </c>
+      <c r="D81" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="17" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="F81" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G81" s="17" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="H81" s="17" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="I81" s="17" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="J81" s="14" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="K81" s="14" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L81" s="14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M81" s="14" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="N81" s="14" t="n">
+        <v>0.182</v>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="73" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="L84" s="4" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="M84" s="4" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="N84" s="4" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>Total Capex ($B)</t>
+        </is>
+      </c>
+      <c r="B85" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C85" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D85" s="21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E85" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F85" s="21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G85" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H85" s="21" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I85" s="21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J85" s="22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="K85" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="L85" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="M85" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="N85" s="22" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>New GW Added</t>
+        </is>
+      </c>
+      <c r="B86" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D86" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F86" s="30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G86" s="30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H86" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I86" s="30" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J86" s="29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K86" s="29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L86" s="29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M86" s="29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N86" s="29" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>Capex / MW Added ($M/MW)</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C87" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D87" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E87" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F87" s="6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G87" s="6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H87" s="6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I87" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="J87" s="7" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="K87" s="7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L87" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="M87" s="7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="N87" s="7" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>Base $/MW (2020 = $9.5M)</t>
+        </is>
+      </c>
+      <c r="B88" s="12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="C88" s="12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D88" s="12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E88" s="12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F88" s="12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G88" s="12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H88" s="12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I88" s="12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J88" s="7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K88" s="7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L88" s="7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M88" s="7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="N88" s="7" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>Volume Effect ($B) [GW x Base $/MW]</t>
+        </is>
+      </c>
+      <c r="B89" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="21" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D89" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="21" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F89" s="21" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G89" s="21" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H89" s="21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I89" s="21" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J89" s="22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="K89" s="22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="L89" s="22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M89" s="22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N89" s="22" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>Price Effect ($B) [GW x Inflation $/MW]</t>
+        </is>
+      </c>
+      <c r="B90" s="23" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C90" s="23" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D90" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F90" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G90" s="23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H90" s="23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I90" s="23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J90" s="22" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="K90" s="22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L90" s="22" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M90" s="22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N90" s="22" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>Other / Maintenance ($B)</t>
+        </is>
+      </c>
+      <c r="B91" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C91" s="21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D91" s="21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E91" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F91" s="21" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="G91" s="21" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="H91" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="I91" s="21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J91" s="22" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="K91" s="22" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="L91" s="22" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="M91" s="22" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="N91" s="22" t="n">
+        <v>15.76</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>Price Inflation % of Capacity Capex</t>
+        </is>
+      </c>
+      <c r="B92" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="17" t="n">
+        <v>-0.056</v>
+      </c>
+      <c r="D92" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F92" s="17" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="G92" s="17" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="H92" s="17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I92" s="17" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="J92" s="14" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="K92" s="14" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="L92" s="14" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="M92" s="14" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="N92" s="14" t="n">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>Industry Aggregate — Total Hyperscaler Capex: Volume vs Price vs Other ($B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="M95" s="4" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="N95" s="4" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>Volume Effect ($B)</t>
+        </is>
+      </c>
+      <c r="B96" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="D96" s="21" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="E96" s="21" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="F96" s="21" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="G96" s="21" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="H96" s="21" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="I96" s="21" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="J96" s="22" t="n">
+        <v>101</v>
+      </c>
+      <c r="K96" s="22" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="L96" s="22" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="M96" s="22" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="N96" s="22" t="n">
+        <v>84.7</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>Price / Inflation Effect ($B)</t>
+        </is>
+      </c>
+      <c r="B97" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" s="23" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="D97" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F97" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G97" s="23" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H97" s="23" t="n">
+        <v>35</v>
+      </c>
+      <c r="I97" s="23" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="J97" s="22" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="K97" s="22" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="L97" s="22" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="M97" s="22" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="N97" s="22" t="n">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>Other / Maintenance ($B)</t>
+        </is>
+      </c>
+      <c r="B98" s="21" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="C98" s="21" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="D98" s="21" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="E98" s="21" t="n">
+        <v>67</v>
+      </c>
+      <c r="F98" s="21" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="G98" s="21" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="H98" s="21" t="n">
+        <v>144.1</v>
+      </c>
+      <c r="I98" s="21" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="J98" s="22" t="n">
+        <v>256.7</v>
+      </c>
+      <c r="K98" s="22" t="n">
+        <v>314</v>
+      </c>
+      <c r="L98" s="22" t="n">
+        <v>352.2</v>
+      </c>
+      <c r="M98" s="22" t="n">
+        <v>385.9</v>
+      </c>
+      <c r="N98" s="22" t="n">
+        <v>409.2</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL HYPERSCALER CAPEX ($B)</t>
+        </is>
+      </c>
+      <c r="B99" s="26" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="C99" s="26" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="D99" s="26" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="E99" s="26" t="n">
+        <v>94</v>
+      </c>
+      <c r="F99" s="26" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="G99" s="26" t="n">
+        <v>154.6</v>
+      </c>
+      <c r="H99" s="26" t="n">
+        <v>254.4</v>
+      </c>
+      <c r="I99" s="26" t="n">
+        <v>361.3</v>
+      </c>
+      <c r="J99" s="26" t="n">
+        <v>410.5</v>
+      </c>
+      <c r="K99" s="26" t="n">
+        <v>461</v>
+      </c>
+      <c r="L99" s="26" t="n">
+        <v>493</v>
+      </c>
+      <c r="M99" s="26" t="n">
+        <v>510.5</v>
+      </c>
+      <c r="N99" s="26" t="n">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>Volume % of Total Capex</t>
+        </is>
+      </c>
+      <c r="B101" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="13" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="D101" s="13" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="E101" s="13" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="F101" s="13" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="G101" s="13" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="H101" s="13" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="I101" s="13" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="J101" s="14" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="K101" s="14" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="L101" s="14" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="M101" s="14" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="N101" s="14" t="n">
+        <v>0.162</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>Price Inflation % of Total Capex</t>
+        </is>
+      </c>
+      <c r="B102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="17" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="17" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F102" s="17" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="G102" s="17" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="H102" s="17" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="I102" s="17" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="J102" s="14" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="K102" s="14" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="L102" s="14" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="M102" s="14" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="N102" s="14" t="n">
+        <v>0.056</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>Other / Maintenance % of Total</t>
+        </is>
+      </c>
+      <c r="B103" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" s="13" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="D103" s="13" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="E103" s="13" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="F103" s="13" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="G103" s="13" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H103" s="13" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="I103" s="13" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="J103" s="14" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="K103" s="14" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="L103" s="14" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="M103" s="14" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="N103" s="14" t="n">
+        <v>0.782</v>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="1">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>Key Component Inflation Drivers &amp; Commentary</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="36" customHeight="1">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B106" s="72" t="inlineStr">
+        <is>
+          <t>GPU / AI ACCELERATORS: Largest single driver of capex inflation; NVIDIA H100/B200 pricing drove index from 100 (2020) to 310 (2024), now declining as AMD MI300/400 competition and next-gen efficiency gains take hold; index projected to reach 140 by 2030 — still 40% above 2020 on price but with 10x more compute per unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="36" customHeight="1">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B107" s="72" t="inlineStr">
+        <is>
+          <t>HV TRANSFORMERS &amp; SWITCHGEAR: Critical bottleneck; lead times extended from 12 months (2020) to 36+ months (2024-2025) driving 85-95% price premiums; index peaked at 195 (2025); new manufacturing capacity (Hitachi, Siemens, ABB) gradually bringing prices down but still elevated through 2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="36" customHeight="1">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B108" s="72" t="inlineStr">
+        <is>
+          <t>CONSTRUCTION LABOR: Sustained inflation due to datacenter construction boom competing for limited skilled electrical/mechanical trades; 48% increase since 2020; expected to remain 38-52% above 2020 levels through 2030 as build volume stays high</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="36" customHeight="1">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B109" s="72" t="inlineStr">
+        <is>
+          <t>LAND &amp; REAL ESTATE: DC-suitable land (power access, fiber, low natural disaster risk) has seen 70-90% appreciation since 2020, especially in Northern Virginia, Phoenix, and Dallas; limited supply in established markets supports sustained premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="36" customHeight="1">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B110" s="72" t="inlineStr">
+        <is>
+          <t>LIQUID COOLING: Opposite trend — prices falling rapidly as technology matures and scales from niche to mainstream; index dropped from 180 (2018) to 62 (2025) and projected to reach 42 by 2030 as immersion/direct-liquid cooling becomes standard for AI racks</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="36" customHeight="1">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B111" s="72" t="inlineStr">
+        <is>
+          <t>CPU SERVERS: Deflationary — consistent ~2-3% annual price declines as Moore's Law continues; AI shift means CPUs are a shrinking share of BOM, partially masking this benefit at the total capex level</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="36" customHeight="1">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B112" s="72" t="inlineStr">
+        <is>
+          <t>NET IMPACT: Weighted-average component inflation peaked at ~45-50% above 2020 levels in 2024-2025; now moderating as GPU prices normalize and transformer supply eases; by 2030 the index is projected at ~15-20% above 2020, meaning roughly 15-20% of capex at that point reflects residual inflation vs where costs were in 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Price Inflation %</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>0</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="I190" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="K190" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="L190" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="M190" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="N190" t="n">
+        <v>0.056</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Volume %</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>0</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="I191" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="K191" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="L191" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="M191" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="N191" t="n">
+        <v>0.162</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="B108:N108"/>
+    <mergeCell ref="A39:N39"/>
+    <mergeCell ref="A83:N83"/>
+    <mergeCell ref="A94:N94"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A61:N61"/>
+    <mergeCell ref="B110:N110"/>
+    <mergeCell ref="B106:N106"/>
+    <mergeCell ref="A25:N25"/>
+    <mergeCell ref="B109:N109"/>
+    <mergeCell ref="A105:N105"/>
+    <mergeCell ref="A50:N50"/>
+    <mergeCell ref="A26:N26"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="B111:N111"/>
+    <mergeCell ref="B107:N107"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="A20:N20"/>
+    <mergeCell ref="A72:N72"/>
+    <mergeCell ref="A28:N28"/>
+    <mergeCell ref="B112:N112"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00999999"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -25300,7 +30625,7 @@
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="73" t="inlineStr">
+      <c r="A3" s="74" t="inlineStr">
         <is>
           <t>Data Sources</t>
         </is>
@@ -25312,7 +30637,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B4" s="74" t="inlineStr">
+      <c r="B4" s="75" t="inlineStr">
         <is>
           <t>2024-2025 capex and revenue actuals from 10-K filings and 4Q25 earnings calls (Jan/Feb 2026)</t>
         </is>
@@ -25324,7 +30649,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B5" s="74" t="inlineStr">
+      <c r="B5" s="75" t="inlineStr">
         <is>
           <t>2026E capex from explicit guidance on 4Q25 earnings calls (Amazon, Microsoft, Google, Meta, Oracle, Apple)</t>
         </is>
@@ -25336,7 +30661,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B6" s="74" t="inlineStr">
+      <c r="B6" s="75" t="inlineStr">
         <is>
           <t>Historical capex and revenue from public SEC filings (10-K, 10-Q) and earnings calls</t>
         </is>
@@ -25348,7 +30673,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B7" s="74" t="inlineStr">
+      <c r="B7" s="75" t="inlineStr">
         <is>
           <t>Server counts estimated from industry reports (Synergy Research, Dell'Oro, Omdia)</t>
         </is>
@@ -25360,7 +30685,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B8" s="74" t="inlineStr">
+      <c r="B8" s="75" t="inlineStr">
         <is>
           <t>Datacenter counts from company announcements, press releases, and analyst estimates</t>
         </is>
@@ -25372,7 +30697,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B9" s="74" t="inlineStr">
+      <c r="B9" s="75" t="inlineStr">
         <is>
           <t>Power capacity from sustainability reports, PPA announcements, and utility filings</t>
         </is>
@@ -25384,7 +30709,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B10" s="74" t="inlineStr">
+      <c r="B10" s="75" t="inlineStr">
         <is>
           <t>Neocloud data from funding announcements, press coverage, and industry estimates</t>
         </is>
@@ -25396,7 +30721,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B11" s="74" t="inlineStr">
+      <c r="B11" s="75" t="inlineStr">
         <is>
           <t>Colo/REIT data from NAREIT filings, investor presentations, and quarterly supplements</t>
         </is>
@@ -25408,7 +30733,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B12" s="74" t="inlineStr">
+      <c r="B12" s="75" t="inlineStr">
         <is>
           <t>Power supply data from EIA, FERC, ISO/RTO reports, and utility IRP filings</t>
         </is>
@@ -25420,7 +30745,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B13" s="74" t="inlineStr">
+      <c r="B13" s="75" t="inlineStr">
         <is>
           <t>BOM costs from construction industry benchmarks, vendor quotes, and DC operator disclosures</t>
         </is>
@@ -25432,14 +30757,14 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B14" s="74" t="inlineStr">
+      <c r="B14" s="75" t="inlineStr">
         <is>
           <t>Supply chain TAM from Gartner, IDC, Dell'Oro, and company-reported revenue segmentation</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="73" t="inlineStr">
+      <c r="A16" s="74" t="inlineStr">
         <is>
           <t>Key Assumptions — Forecasts (2025E-2030E)</t>
         </is>
@@ -25451,7 +30776,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B17" s="74" t="inlineStr">
+      <c r="B17" s="75" t="inlineStr">
         <is>
           <t>AI infrastructure buildout continues to accelerate through 2027, moderating thereafter</t>
         </is>
@@ -25463,7 +30788,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B18" s="74" t="inlineStr">
+      <c r="B18" s="75" t="inlineStr">
         <is>
           <t>Hyperscaler capex growth driven by AI/ML workloads, sovereign cloud, and edge expansion</t>
         </is>
@@ -25475,7 +30800,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B19" s="74" t="inlineStr">
+      <c r="B19" s="75" t="inlineStr">
         <is>
           <t>Neocloud vendors benefit from GPU-as-a-service demand but face capital constraints</t>
         </is>
@@ -25487,7 +30812,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B20" s="74" t="inlineStr">
+      <c r="B20" s="75" t="inlineStr">
         <is>
           <t>Colo/REIT capex accelerates as hyperscalers increasingly lease rather than build</t>
         </is>
@@ -25499,7 +30824,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B21" s="74" t="inlineStr">
+      <c r="B21" s="75" t="inlineStr">
         <is>
           <t>Power availability is the key constraint on datacenter buildout after 2026</t>
         </is>
@@ -25511,7 +30836,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B22" s="74" t="inlineStr">
+      <c r="B22" s="75" t="inlineStr">
         <is>
           <t>Renewable energy targets: most hyperscalers reach 100% by 2027-2030</t>
         </is>
@@ -25523,7 +30848,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B23" s="74" t="inlineStr">
+      <c r="B23" s="75" t="inlineStr">
         <is>
           <t>Server density improves 8-12% annually (more compute per rack unit)</t>
         </is>
@@ -25535,7 +30860,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B24" s="74" t="inlineStr">
+      <c r="B24" s="75" t="inlineStr">
         <is>
           <t>Average PUE improves from ~1.3 (2024) to ~1.15 (2030) industry-wide</t>
         </is>
@@ -25547,7 +30872,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B25" s="74" t="inlineStr">
+      <c r="B25" s="75" t="inlineStr">
         <is>
           <t>SMR/advanced nuclear begins contributing meaningfully after 2028</t>
         </is>
@@ -25559,14 +30884,14 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B26" s="74" t="inlineStr">
+      <c r="B26" s="75" t="inlineStr">
         <is>
           <t>Transformer lead times peak in 2025-2026, gradually improve as manufacturing scales</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="73" t="inlineStr">
+      <c r="A28" s="74" t="inlineStr">
         <is>
           <t>Power Supply Assumptions</t>
         </is>
@@ -25578,7 +30903,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B29" s="74" t="inlineStr">
+      <c r="B29" s="75" t="inlineStr">
         <is>
           <t>Natural gas remains the primary source for near-term DC power additions through 2027</t>
         </is>
@@ -25590,7 +30915,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B30" s="74" t="inlineStr">
+      <c r="B30" s="75" t="inlineStr">
         <is>
           <t>Solar + battery storage combinations become cost-competitive for 24/7 DC power by 2028</t>
         </is>
@@ -25602,7 +30927,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B31" s="74" t="inlineStr">
+      <c r="B31" s="75" t="inlineStr">
         <is>
           <t>Nuclear (SMR) first commercial deployments for DC use begin in 2027-2028</t>
         </is>
@@ -25614,7 +30939,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B32" s="74" t="inlineStr">
+      <c r="B32" s="75" t="inlineStr">
         <is>
           <t>Grid interconnection queue times peak at ~42 months in 2025E, declining as processes streamline</t>
         </is>
@@ -25626,7 +30951,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B33" s="74" t="inlineStr">
+      <c r="B33" s="75" t="inlineStr">
         <is>
           <t>Average DC power cost peaks at ~$72/MWh in 2025E before declining with renewables scale</t>
         </is>
@@ -25638,14 +30963,14 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B34" s="74" t="inlineStr">
+      <c r="B34" s="75" t="inlineStr">
         <is>
           <t>Behind-the-meter generation (on-site solar, fuel cells) grows from &lt;5% to ~15% by 2030</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="73" t="inlineStr">
+      <c r="A36" s="74" t="inlineStr">
         <is>
           <t>Bill of Materials Assumptions</t>
         </is>
@@ -25657,7 +30982,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B37" s="74" t="inlineStr">
+      <c r="B37" s="75" t="inlineStr">
         <is>
           <t>BOM costs reflect average hyperscale build; enterprise/colo builds may differ by 20-30%</t>
         </is>
@@ -25669,7 +30994,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B38" s="74" t="inlineStr">
+      <c r="B38" s="75" t="inlineStr">
         <is>
           <t>GPU server costs assume mix of NVIDIA H100/B200/next-gen accelerators at typical deployment ratios</t>
         </is>
@@ -25681,7 +31006,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B39" s="74" t="inlineStr">
+      <c r="B39" s="75" t="inlineStr">
         <is>
           <t>Liquid cooling penetration grows from ~10% of new builds (2024) to ~60% (2030E) for AI-heavy facilities</t>
         </is>
@@ -25693,7 +31018,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B40" s="74" t="inlineStr">
+      <c r="B40" s="75" t="inlineStr">
         <is>
           <t>Electrical infrastructure costs include transformer premiums from current supply shortage</t>
         </is>
@@ -25705,14 +31030,14 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B41" s="74" t="inlineStr">
+      <c r="B41" s="75" t="inlineStr">
         <is>
           <t>Construction labor cost inflation of ~3-5% annually, partially offset by modular/prefab methods</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="73" t="inlineStr">
+      <c r="A43" s="74" t="inlineStr">
         <is>
           <t>Supply Chain Assumptions</t>
         </is>
@@ -25724,7 +31049,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B44" s="74" t="inlineStr">
+      <c r="B44" s="75" t="inlineStr">
         <is>
           <t>TAM figures represent addressable market for DC-specific spend (not total vendor revenue)</t>
         </is>
@@ -25736,7 +31061,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B45" s="74" t="inlineStr">
+      <c r="B45" s="75" t="inlineStr">
         <is>
           <t>Servers &amp; GPUs segment is the largest and fastest-growing, driven by AI accelerator demand</t>
         </is>
@@ -25748,7 +31073,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B46" s="74" t="inlineStr">
+      <c r="B46" s="75" t="inlineStr">
         <is>
           <t>Supply chain TAM exceeds operator capex because it includes maintenance, refresh, and software</t>
         </is>
@@ -25760,7 +31085,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B47" s="74" t="inlineStr">
+      <c r="B47" s="75" t="inlineStr">
         <is>
           <t>Revenue multiplier (TAM/Capex) reflects that capex flows through multiple vendor layers</t>
         </is>
@@ -25772,16 +31097,16 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B48" s="74" t="inlineStr">
+      <c r="B48" s="75" t="inlineStr">
         <is>
           <t>Key supply chain bottlenecks: GPU supply, transformer manufacturing, skilled labor, power</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="73" t="inlineStr">
-        <is>
-          <t>AI Capex-to-Revenue Assumptions</t>
+      <c r="A50" s="74" t="inlineStr">
+        <is>
+          <t>Capex Decomposition Assumptions</t>
         </is>
       </c>
     </row>
@@ -25791,9 +31116,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B51" s="74" t="inlineStr">
-        <is>
-          <t>AI Capex = portion of total capex allocated to GPU clusters, AI networking, liquid cooling for AI, AI-dedicated DCs</t>
+      <c r="B51" s="75" t="inlineStr">
+        <is>
+          <t>Component price indices use 2020 as base year (index = 100); chosen because 2020 was pre-inflation, pre-AI-boom baseline</t>
         </is>
       </c>
     </row>
@@ -25803,9 +31128,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B52" s="74" t="inlineStr">
-        <is>
-          <t>AI Revenue = revenue directly attributable to AI: cloud AI services (hyperscalers), GPU-as-a-service (neoclouds), AI tenant leases (colo/REITs)</t>
+      <c r="B52" s="75" t="inlineStr">
+        <is>
+          <t>GPU/AI Accelerator index reflects weighted-average price of datacenter GPUs (H100, A100, B200 equivalent); rose sharply 2021-2024 on NVIDIA pricing power, now moderating with AMD competition and next-gen efficiency</t>
         </is>
       </c>
     </row>
@@ -25815,9 +31140,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B53" s="74" t="inlineStr">
-        <is>
-          <t>Meta AI revenue represents estimated uplift to advertising revenue from AI-powered recommendation and targeting improvements</t>
+      <c r="B53" s="75" t="inlineStr">
+        <is>
+          <t>HV Transformer index reflects 85-95% price premium vs 2020 driven by 36+ month lead times; new manufacturing capacity (Hitachi, Siemens, ABB) gradually easing supply by 2027-2028</t>
         </is>
       </c>
     </row>
@@ -25827,9 +31152,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B54" s="74" t="inlineStr">
-        <is>
-          <t>Apple AI revenue reflects Apple Intelligence services, Siri improvements, and AI-enhanced services revenue uplift</t>
+      <c r="B54" s="75" t="inlineStr">
+        <is>
+          <t>Weighted-average index uses 2024 BOM cost shares as weights: GPU/AI 30%, CPU 12%, construction 10%, networking 9%, transformers 7%, land 6%, etc.</t>
         </is>
       </c>
     </row>
@@ -25839,9 +31164,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B55" s="74" t="inlineStr">
-        <is>
-          <t>Oracle AI revenue driven by OCI GPU superclusters, Autonomous Database AI features, and AI cloud infrastructure</t>
+      <c r="B55" s="75" t="inlineStr">
+        <is>
+          <t>Capex decomposition uses formula: Total Capex = (New GW x Base $/MW) + (New GW x Inflation $/MW) + Other/Maintenance</t>
         </is>
       </c>
     </row>
@@ -25851,9 +31176,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B56" s="74" t="inlineStr">
-        <is>
-          <t>Capex-to-revenue lag varies by business model: neoclouds ~4 qtrs (direct GPU lease), hyperscalers ~5-8 qtrs (build→GA→ramp), colo ~6-7 qtrs (lease negotiation)</t>
+      <c r="B56" s="75" t="inlineStr">
+        <is>
+          <t>Base $/MW is frozen at each company's 2020 cost per MW of new capacity; inflation $/MW = current cost/MW minus base</t>
         </is>
       </c>
     </row>
@@ -25863,9 +31188,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B57" s="74" t="inlineStr">
-        <is>
-          <t>Cumulative payback year = first year where cumulative AI revenue &gt;= cumulative AI capex since inception</t>
+      <c r="B57" s="75" t="inlineStr">
+        <is>
+          <t>'Other/Maintenance' includes sustaining capex on existing facilities, non-capacity investments, and any residual not captured by the volume x price model</t>
         </is>
       </c>
     </row>
@@ -25875,9 +31200,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B58" s="74" t="inlineStr">
-        <is>
-          <t>Annual AI Rev/Capex ratio &gt;1.0x indicates that year's AI revenue exceeds that year's AI capex investment</t>
+      <c r="B58" s="75" t="inlineStr">
+        <is>
+          <t>Liquid cooling is the only major component with sustained deflation — prices falling ~15-20% annually as technology matures from niche to standard</t>
         </is>
       </c>
     </row>
@@ -25887,16 +31212,16 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B59" s="74" t="inlineStr">
-        <is>
-          <t>Payback analysis does not account for depreciation, opex, or cost of capital; represents gross capex recovery only</t>
+      <c r="B59" s="75" t="inlineStr">
+        <is>
+          <t>Peak industry-wide component inflation was 2024-2025; moderating through 2030 but not returning to 2020 levels (structural premiums in land, labor, GPUs remain)</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="73" t="inlineStr">
-        <is>
-          <t>Colocation / REIT Assumptions</t>
+      <c r="A61" s="74" t="inlineStr">
+        <is>
+          <t>AI Capex-to-Revenue Assumptions</t>
         </is>
       </c>
     </row>
@@ -25906,9 +31231,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B62" s="74" t="inlineStr">
-        <is>
-          <t>Equinix, Digital Realty data from public REIT filings and investor supplements</t>
+      <c r="B62" s="75" t="inlineStr">
+        <is>
+          <t>AI Capex = portion of total capex allocated to GPU clusters, AI networking, liquid cooling for AI, AI-dedicated DCs</t>
         </is>
       </c>
     </row>
@@ -25918,9 +31243,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B63" s="74" t="inlineStr">
-        <is>
-          <t>CyrusOne (KKR/GIP) and QTS (Blackstone) data estimated post-acquisition from industry reports</t>
+      <c r="B63" s="75" t="inlineStr">
+        <is>
+          <t>AI Revenue = revenue directly attributable to AI: cloud AI services (hyperscalers), GPU-as-a-service (neoclouds), AI tenant leases (colo/REITs)</t>
         </is>
       </c>
     </row>
@@ -25930,9 +31255,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B64" s="74" t="inlineStr">
-        <is>
-          <t>Vantage and Switch data from press releases, funding announcements, and analyst estimates</t>
+      <c r="B64" s="75" t="inlineStr">
+        <is>
+          <t>Meta AI revenue represents estimated uplift to advertising revenue from AI-powered recommendation and targeting improvements</t>
         </is>
       </c>
     </row>
@@ -25942,9 +31267,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B65" s="74" t="inlineStr">
-        <is>
-          <t>Colo revenue is facility/leasing revenue; does not include cloud service revenue</t>
+      <c r="B65" s="75" t="inlineStr">
+        <is>
+          <t>Apple AI revenue reflects Apple Intelligence services, Siri improvements, and AI-enhanced services revenue uplift</t>
         </is>
       </c>
     </row>
@@ -25954,9 +31279,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B66" s="74" t="inlineStr">
-        <is>
-          <t>DC counts for Colo/REITs include all owned and operated facilities globally</t>
+      <c r="B66" s="75" t="inlineStr">
+        <is>
+          <t>Oracle AI revenue driven by OCI GPU superclusters, Autonomous Database AI features, and AI cloud infrastructure</t>
         </is>
       </c>
     </row>
@@ -25966,16 +31291,33 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B67" s="74" t="inlineStr">
-        <is>
-          <t>Server counts for Colo/REITs represent customer-deployed servers hosted in their facilities</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="73" t="inlineStr">
-        <is>
-          <t>Definitions</t>
+      <c r="B67" s="75" t="inlineStr">
+        <is>
+          <t>Capex-to-revenue lag varies by business model: neoclouds ~4 qtrs (direct GPU lease), hyperscalers ~5-8 qtrs (build→GA→ramp), colo ~6-7 qtrs (lease negotiation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B68" s="75" t="inlineStr">
+        <is>
+          <t>Cumulative payback year = first year where cumulative AI revenue &gt;= cumulative AI capex since inception</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B69" s="75" t="inlineStr">
+        <is>
+          <t>Annual AI Rev/Capex ratio &gt;1.0x indicates that year's AI revenue exceeds that year's AI capex investment</t>
         </is>
       </c>
     </row>
@@ -25985,33 +31327,16 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B70" s="74" t="inlineStr">
-        <is>
-          <t>IT Load (GW): Total electrical power consumed by IT equipment (servers, storage, networking)</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B71" s="74" t="inlineStr">
-        <is>
-          <t>Power Contracted (GW): Total power capacity secured via PPAs, utility contracts, and on-site generation</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B72" s="74" t="inlineStr">
-        <is>
-          <t>Power Utilization: IT Load / Power Contracted (higher = more efficient use of secured power)</t>
+      <c r="B70" s="75" t="inlineStr">
+        <is>
+          <t>Payback analysis does not account for depreciation, opex, or cost of capital; represents gross capex recovery only</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="74" t="inlineStr">
+        <is>
+          <t>Colocation / REIT Assumptions</t>
         </is>
       </c>
     </row>
@@ -26021,9 +31346,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B73" s="74" t="inlineStr">
-        <is>
-          <t>Revenue/MW: Annual revenue ($B) / IT Load (GW); result is in $M/MW (since 1 GW = 1000 MW)</t>
+      <c r="B73" s="75" t="inlineStr">
+        <is>
+          <t>Equinix, Digital Realty data from public REIT filings and investor supplements</t>
         </is>
       </c>
     </row>
@@ -26033,9 +31358,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B74" s="74" t="inlineStr">
-        <is>
-          <t>Capex/MW: Annual capex ($B) / IT Load (GW) — investment intensity per MW of IT capacity</t>
+      <c r="B74" s="75" t="inlineStr">
+        <is>
+          <t>CyrusOne (KKR/GIP) and QTS (Blackstone) data estimated post-acquisition from industry reports</t>
         </is>
       </c>
     </row>
@@ -26045,9 +31370,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B75" s="74" t="inlineStr">
-        <is>
-          <t>Servers (000s): Total server count in thousands across all datacenter locations</t>
+      <c r="B75" s="75" t="inlineStr">
+        <is>
+          <t>Vantage and Switch data from press releases, funding announcements, and analyst estimates</t>
         </is>
       </c>
     </row>
@@ -26057,9 +31382,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B76" s="74" t="inlineStr">
-        <is>
-          <t>TAM: Total Addressable Market — revenue opportunity for vendors in each supply chain segment</t>
+      <c r="B76" s="75" t="inlineStr">
+        <is>
+          <t>Colo revenue is facility/leasing revenue; does not include cloud service revenue</t>
         </is>
       </c>
     </row>
@@ -26069,9 +31394,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B77" s="74" t="inlineStr">
-        <is>
-          <t>BOM: Bill of Materials — component and construction cost breakdown per MW of IT load</t>
+      <c r="B77" s="75" t="inlineStr">
+        <is>
+          <t>DC counts for Colo/REITs include all owned and operated facilities globally</t>
         </is>
       </c>
     </row>
@@ -26081,33 +31406,16 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B78" s="74" t="inlineStr">
-        <is>
-          <t>AI Capex: Portion of total capex allocated specifically to AI/ML infrastructure (GPU clusters, AI networking, liquid cooling)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B79" s="74" t="inlineStr">
-        <is>
-          <t>AI Revenue: Revenue directly attributable to AI products and services (cloud AI, GPU-as-a-service, AI tenant leases)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B80" s="74" t="inlineStr">
-        <is>
-          <t>Cumulative Payback: Year when cumulative AI revenue first exceeds cumulative AI capex since inception</t>
+      <c r="B78" s="75" t="inlineStr">
+        <is>
+          <t>Server counts for Colo/REITs represent customer-deployed servers hosted in their facilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="74" t="inlineStr">
+        <is>
+          <t>Definitions</t>
         </is>
       </c>
     </row>
@@ -26117,16 +31425,33 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B81" s="74" t="inlineStr">
-        <is>
-          <t>AI Rev/Capex Ratio: Annual AI revenue divided by annual AI capex; &gt;1.0x means AI revenue exceeds AI investment in that year</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="22" customHeight="1">
-      <c r="A83" s="73" t="inlineStr">
-        <is>
-          <t>Caveats</t>
+      <c r="B81" s="75" t="inlineStr">
+        <is>
+          <t>IT Load (GW): Total electrical power consumed by IT equipment (servers, storage, networking)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B82" s="75" t="inlineStr">
+        <is>
+          <t>Power Contracted (GW): Total power capacity secured via PPAs, utility contracts, and on-site generation</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B83" s="75" t="inlineStr">
+        <is>
+          <t>Power Utilization: IT Load / Power Contracted (higher = more efficient use of secured power)</t>
         </is>
       </c>
     </row>
@@ -26136,9 +31461,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B84" s="74" t="inlineStr">
-        <is>
-          <t>All neocloud figures are estimates based on limited public disclosure</t>
+      <c r="B84" s="75" t="inlineStr">
+        <is>
+          <t>Revenue/MW: Annual revenue ($B) / IT Load (GW); result is in $M/MW (since 1 GW = 1000 MW)</t>
         </is>
       </c>
     </row>
@@ -26148,9 +31473,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B85" s="74" t="inlineStr">
-        <is>
-          <t>Company-specific DC counts may include leased/colocation facilities</t>
+      <c r="B85" s="75" t="inlineStr">
+        <is>
+          <t>Capex/MW: Annual capex ($B) / IT Load (GW) — investment intensity per MW of IT capacity</t>
         </is>
       </c>
     </row>
@@ -26160,9 +31485,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B86" s="74" t="inlineStr">
-        <is>
-          <t>Apple revenue is total company revenue (not cloud-specific); DC figures are for internal use</t>
+      <c r="B86" s="75" t="inlineStr">
+        <is>
+          <t>Servers (000s): Total server count in thousands across all datacenter locations</t>
         </is>
       </c>
     </row>
@@ -26172,9 +31497,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B87" s="74" t="inlineStr">
-        <is>
-          <t>Meta revenue is total company revenue; DC infrastructure supports ads + AI workloads</t>
+      <c r="B87" s="75" t="inlineStr">
+        <is>
+          <t>TAM: Total Addressable Market — revenue opportunity for vendors in each supply chain segment</t>
         </is>
       </c>
     </row>
@@ -26184,9 +31509,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B88" s="74" t="inlineStr">
-        <is>
-          <t>CyrusOne and QTS are now private; post-acquisition data are estimates</t>
+      <c r="B88" s="75" t="inlineStr">
+        <is>
+          <t>BOM: Bill of Materials — component and construction cost breakdown per MW of IT load</t>
         </is>
       </c>
     </row>
@@ -26196,9 +31521,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B89" s="74" t="inlineStr">
-        <is>
-          <t>Forecasts represent base-case scenario; upside/downside cases not included</t>
+      <c r="B89" s="75" t="inlineStr">
+        <is>
+          <t>AI Capex: Portion of total capex allocated specifically to AI/ML infrastructure (GPU clusters, AI networking, liquid cooling)</t>
         </is>
       </c>
     </row>
@@ -26208,20 +31533,136 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B90" s="74" t="inlineStr">
+      <c r="B90" s="75" t="inlineStr">
+        <is>
+          <t>AI Revenue: Revenue directly attributable to AI products and services (cloud AI, GPU-as-a-service, AI tenant leases)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B91" s="75" t="inlineStr">
+        <is>
+          <t>Cumulative Payback: Year when cumulative AI revenue first exceeds cumulative AI capex since inception</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B92" s="75" t="inlineStr">
+        <is>
+          <t>AI Rev/Capex Ratio: Annual AI revenue divided by annual AI capex; &gt;1.0x means AI revenue exceeds AI investment in that year</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="74" t="inlineStr">
+        <is>
+          <t>Caveats</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B95" s="75" t="inlineStr">
+        <is>
+          <t>All neocloud figures are estimates based on limited public disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B96" s="75" t="inlineStr">
+        <is>
+          <t>Company-specific DC counts may include leased/colocation facilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B97" s="75" t="inlineStr">
+        <is>
+          <t>Apple revenue is total company revenue (not cloud-specific); DC figures are for internal use</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B98" s="75" t="inlineStr">
+        <is>
+          <t>Meta revenue is total company revenue; DC infrastructure supports ads + AI workloads</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B99" s="75" t="inlineStr">
+        <is>
+          <t>CyrusOne and QTS are now private; post-acquisition data are estimates</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B100" s="75" t="inlineStr">
+        <is>
+          <t>Forecasts represent base-case scenario; upside/downside cases not included</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B101" s="75" t="inlineStr">
         <is>
           <t>Currency: All figures in USD</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A80:H80"/>
+    <mergeCell ref="A94:H94"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A69:H69"/>
-    <mergeCell ref="A83:H83"/>
     <mergeCell ref="A43:H43"/>
     <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A72:H72"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A1:H1"/>

--- a/Datacenter_Infrastructure_Model.xlsx
+++ b/Datacenter_Infrastructure_Model.xlsx
@@ -20,7 +20,8 @@
     <sheet name="Capex to Revenue" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Capex to AI Revenue" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Capex Decomposition" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Assumptions &amp; Sources" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="ROIC Analysis" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Assumptions &amp; Sources" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -194,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -412,6 +413,12 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -9771,6 +9778,954 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart56.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>ROIC (%) — Hyperscalers (AI Revenue Based)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$66:$N$66</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$67:$N$67</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$68:$N$68</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$69:$N$69</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$70:$N$70</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="FF6384"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$71:$N$71</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart57.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>ROIC (%) — Neoclouds (Total Revenue Based)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$72:$N$72</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$73:$N$73</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$74:$N$74</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$75:$N$75</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$76:$N$76</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="FF6384"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$77:$N$77</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart58.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>NOPAT ($B) — Key Companies</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$36:$N$36</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$37:$N$37</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$38:$N$38</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$39:$N$39</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$40:$N$40</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="FF6384"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$42:$N$42</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart59.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Net Invested Capital ($B) — Key Companies</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$51:$N$51</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$52:$N$52</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$53:$N$53</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$54:$N$54</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$55:$N$55</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="FF6384"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$57:$N$57</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
@@ -9940,6 +10895,480 @@
           <val>
             <numRef>
               <f>'Capex Spend'!$B$20:$N$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart60.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Incremental ROIC (%) — Hyperscalers</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$66:$N$66</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$67:$N$67</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$68:$N$68</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$69:$N$69</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$70:$N$70</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="FF6384"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$71:$N$71</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart61.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>AI Operating Margins (%) — Key Companies</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$21:$N$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$22:$N$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$23:$N$23</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$24:$N$24</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$25:$N$25</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="FF6384"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'ROIC Analysis'!$B$27:$N$27</f>
             </numRef>
           </val>
         </ser>
@@ -11080,6 +12509,143 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>120</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9360000" cy="5400000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>120</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="5400000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>137</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9360000" cy="5400000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>137</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="5400000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>154</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9360000" cy="5400000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>154</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="5400000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="6" name="Chart 6"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -30606,11 +32172,4433 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00006100"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N118"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Return on Invested Capital (ROIC) — AI Revenue for Hyperscalers, Total Revenue for Neoclouds</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="33" t="inlineStr">
+        <is>
+          <t>ROIC = NOPAT / Invested Capital  |  NOPAT = AI Op. Income x (1 - Tax)  |  Invested Capital = Cum. AI Capex - Accum. Depreciation  |  Yellow = 2026E+ Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Revenue Base ($B) — AI Revenue for Hyperscalers, Total Revenue for Neoclouds</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Amazon (AWS)</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D6" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F6" s="21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G6" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H6" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="I6" s="21" t="n">
+        <v>35</v>
+      </c>
+      <c r="J6" s="22" t="n">
+        <v>54</v>
+      </c>
+      <c r="K6" s="22" t="n">
+        <v>76</v>
+      </c>
+      <c r="L6" s="22" t="n">
+        <v>98</v>
+      </c>
+      <c r="M6" s="22" t="n">
+        <v>124</v>
+      </c>
+      <c r="N6" s="22" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Microsoft (Azure)</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D7" s="23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E7" s="23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" s="23" t="n">
+        <v>25</v>
+      </c>
+      <c r="I7" s="23" t="n">
+        <v>46</v>
+      </c>
+      <c r="J7" s="22" t="n">
+        <v>72</v>
+      </c>
+      <c r="K7" s="22" t="n">
+        <v>98</v>
+      </c>
+      <c r="L7" s="22" t="n">
+        <v>126</v>
+      </c>
+      <c r="M7" s="22" t="n">
+        <v>156</v>
+      </c>
+      <c r="N7" s="22" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Google (GCP)</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D8" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G8" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="I8" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="J8" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="K8" s="22" t="n">
+        <v>55</v>
+      </c>
+      <c r="L8" s="22" t="n">
+        <v>72</v>
+      </c>
+      <c r="M8" s="22" t="n">
+        <v>88</v>
+      </c>
+      <c r="N8" s="22" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D9" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="H9" s="23" t="n">
+        <v>32</v>
+      </c>
+      <c r="I9" s="23" t="n">
+        <v>52</v>
+      </c>
+      <c r="J9" s="22" t="n">
+        <v>70</v>
+      </c>
+      <c r="K9" s="22" t="n">
+        <v>88</v>
+      </c>
+      <c r="L9" s="22" t="n">
+        <v>105</v>
+      </c>
+      <c r="M9" s="22" t="n">
+        <v>122</v>
+      </c>
+      <c r="N9" s="22" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Oracle Cloud</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F10" s="21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G10" s="21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H10" s="21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I10" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="J10" s="22" t="n">
+        <v>19</v>
+      </c>
+      <c r="K10" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="L10" s="22" t="n">
+        <v>32</v>
+      </c>
+      <c r="M10" s="22" t="n">
+        <v>38</v>
+      </c>
+      <c r="N10" s="22" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E11" s="23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J11" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="K11" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="L11" s="22" t="n">
+        <v>23</v>
+      </c>
+      <c r="M11" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="N11" s="22" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I12" s="21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J12" s="22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K12" s="22" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L12" s="22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="M12" s="22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="N12" s="22" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Lambda</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G13" s="23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H13" s="23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I13" s="23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J13" s="22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K13" s="22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L13" s="22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M13" s="22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N13" s="22" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Crusoe Energy</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H14" s="21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I14" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J14" s="22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K14" s="22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L14" s="22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M14" s="22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N14" s="22" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Voltage Park</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="23" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H15" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I15" s="23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J15" s="22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K15" s="22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L15" s="22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M15" s="22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N15" s="22" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Together AI</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="21" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H16" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I16" s="21" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J16" s="22" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K16" s="22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L16" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="N16" s="22" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Applied Digital</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="23" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G17" s="23" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H17" s="23" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I17" s="23" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J17" s="22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K17" s="22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L17" s="22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M17" s="22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N17" s="22" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Operating Margin on AI/Cloud Revenue (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Amazon (AWS)</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I21" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K21" s="14" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="L21" s="14" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M21" s="14" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N21" s="14" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Microsoft (Azure)</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G22" s="17" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K22" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L22" s="14" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M22" s="14" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N22" s="14" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Google (GCP)</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H23" s="13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I23" s="13" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K23" s="14" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L23" s="14" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M23" s="14" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="N23" s="14" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G24" s="17" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I24" s="17" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K24" s="14" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L24" s="14" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M24" s="14" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="N24" s="14" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Oracle Cloud</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I25" s="13" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K25" s="14" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L25" s="14" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M25" s="14" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N25" s="14" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F26" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G26" s="17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H26" s="17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I26" s="17" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J26" s="14" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K26" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L26" s="14" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M26" s="14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N26" s="14" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I27" s="13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J27" s="14" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K27" s="14" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="L27" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M27" s="14" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="N27" s="14" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Lambda</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="17" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="G28" s="17" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H28" s="17" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I28" s="17" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J28" s="14" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K28" s="14" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L28" s="14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M28" s="14" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="N28" s="14" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Crusoe Energy</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H29" s="13" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I29" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K29" s="14" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L29" s="14" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M29" s="14" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="N29" s="14" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Voltage Park</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="17" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="H30" s="17" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="I30" s="17" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J30" s="14" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K30" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L30" s="14" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M30" s="14" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N30" s="14" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Together AI</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="H31" s="13" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="I31" s="13" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J31" s="14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K31" s="14" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L31" s="14" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M31" s="14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N31" s="14" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Applied Digital</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="17" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G32" s="17" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="H32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J32" s="14" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K32" s="14" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L32" s="14" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M32" s="14" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="N32" s="14" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>NOPAT ($B) — Net Operating Profit After Tax [Revenue x Margin x (1 - 21% Tax)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Amazon (AWS)</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D36" s="21" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E36" s="21" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F36" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G36" s="21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H36" s="21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I36" s="21" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="J36" s="22" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="K36" s="22" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="L36" s="22" t="n">
+        <v>27.87</v>
+      </c>
+      <c r="M36" s="22" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="N36" s="22" t="n">
+        <v>45.63</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Microsoft (Azure)</t>
+        </is>
+      </c>
+      <c r="B37" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="23" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E37" s="23" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F37" s="23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G37" s="23" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="H37" s="23" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="I37" s="23" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="J37" s="22" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="K37" s="22" t="n">
+        <v>30.97</v>
+      </c>
+      <c r="L37" s="22" t="n">
+        <v>41.81</v>
+      </c>
+      <c r="M37" s="22" t="n">
+        <v>52.99</v>
+      </c>
+      <c r="N37" s="22" t="n">
+        <v>65.34999999999999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Google (GCP)</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E38" s="21" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F38" s="21" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G38" s="21" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H38" s="21" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="I38" s="21" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="J38" s="22" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="K38" s="22" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="L38" s="22" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="M38" s="22" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="N38" s="22" t="n">
+        <v>31.52</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B39" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="23" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D39" s="23" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E39" s="23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F39" s="23" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="G39" s="23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H39" s="23" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="I39" s="23" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="J39" s="22" t="n">
+        <v>24.89</v>
+      </c>
+      <c r="K39" s="22" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="L39" s="22" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="M39" s="22" t="n">
+        <v>46.26</v>
+      </c>
+      <c r="N39" s="22" t="n">
+        <v>53.09</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Oracle Cloud</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G40" s="21" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H40" s="21" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I40" s="21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J40" s="22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K40" s="22" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="L40" s="22" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="M40" s="22" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="N40" s="22" t="n">
+        <v>13.21</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="B41" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E41" s="23" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F41" s="23" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G41" s="23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H41" s="23" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="I41" s="23" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="J41" s="22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K41" s="22" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="L41" s="22" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="M41" s="22" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="N41" s="22" t="n">
+        <v>13.51</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="B42" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="21" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G42" s="21" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="H42" s="21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I42" s="21" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J42" s="22" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K42" s="22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L42" s="22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="M42" s="22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N42" s="22" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Lambda</t>
+        </is>
+      </c>
+      <c r="B43" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G43" s="23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="H43" s="23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I43" s="23" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J43" s="22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K43" s="22" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L43" s="22" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M43" s="22" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="N43" s="22" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Crusoe Energy</t>
+        </is>
+      </c>
+      <c r="B44" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="21" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G44" s="21" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="H44" s="21" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I44" s="21" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J44" s="22" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K44" s="22" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L44" s="22" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="M44" s="22" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N44" s="22" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Voltage Park</t>
+        </is>
+      </c>
+      <c r="B45" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="H45" s="23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I45" s="23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J45" s="22" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K45" s="22" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L45" s="22" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M45" s="22" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="N45" s="22" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Together AI</t>
+        </is>
+      </c>
+      <c r="B46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="21" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="H46" s="21" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I46" s="21" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="J46" s="22" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K46" s="22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L46" s="22" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M46" s="22" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="N46" s="22" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Applied Digital</t>
+        </is>
+      </c>
+      <c r="B47" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="23" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G47" s="23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="H47" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="23" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J47" s="22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K47" s="22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L47" s="22" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M47" s="22" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="N47" s="22" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Invested Capital ($B) — Cumulative AI Capex Less Accumulated Depreciation (7yr avg life)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Amazon (AWS)</t>
+        </is>
+      </c>
+      <c r="B51" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C51" s="21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D51" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F51" s="21" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G51" s="21" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="H51" s="21" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="I51" s="21" t="n">
+        <v>114.9</v>
+      </c>
+      <c r="J51" s="22" t="n">
+        <v>166</v>
+      </c>
+      <c r="K51" s="22" t="n">
+        <v>223.2</v>
+      </c>
+      <c r="L51" s="22" t="n">
+        <v>279.4</v>
+      </c>
+      <c r="M51" s="22" t="n">
+        <v>327.3</v>
+      </c>
+      <c r="N51" s="22" t="n">
+        <v>365.6</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Microsoft (Azure)</t>
+        </is>
+      </c>
+      <c r="B52" s="23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C52" s="23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D52" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E52" s="23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F52" s="23" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G52" s="23" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="H52" s="23" t="n">
+        <v>53</v>
+      </c>
+      <c r="I52" s="23" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="J52" s="22" t="n">
+        <v>151.9</v>
+      </c>
+      <c r="K52" s="22" t="n">
+        <v>203.7</v>
+      </c>
+      <c r="L52" s="22" t="n">
+        <v>252.6</v>
+      </c>
+      <c r="M52" s="22" t="n">
+        <v>293.7</v>
+      </c>
+      <c r="N52" s="22" t="n">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Google (GCP)</t>
+        </is>
+      </c>
+      <c r="B53" s="21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C53" s="21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D53" s="21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E53" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="F53" s="21" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="G53" s="21" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="H53" s="21" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="I53" s="21" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="J53" s="22" t="n">
+        <v>133.4</v>
+      </c>
+      <c r="K53" s="22" t="n">
+        <v>176</v>
+      </c>
+      <c r="L53" s="22" t="n">
+        <v>215.5</v>
+      </c>
+      <c r="M53" s="22" t="n">
+        <v>249.3</v>
+      </c>
+      <c r="N53" s="22" t="n">
+        <v>275.2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B54" s="23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C54" s="23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D54" s="23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E54" s="23" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F54" s="23" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="G54" s="23" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="H54" s="23" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="I54" s="23" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="J54" s="22" t="n">
+        <v>137.1</v>
+      </c>
+      <c r="K54" s="22" t="n">
+        <v>174.7</v>
+      </c>
+      <c r="L54" s="22" t="n">
+        <v>205.9</v>
+      </c>
+      <c r="M54" s="22" t="n">
+        <v>229.6</v>
+      </c>
+      <c r="N54" s="22" t="n">
+        <v>246.1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Oracle Cloud</t>
+        </is>
+      </c>
+      <c r="B55" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E55" s="21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F55" s="21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G55" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H55" s="21" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I55" s="21" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="J55" s="22" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="K55" s="22" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="L55" s="22" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="M55" s="22" t="n">
+        <v>81</v>
+      </c>
+      <c r="N55" s="22" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="B56" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C56" s="23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D56" s="23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E56" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G56" s="23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H56" s="23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I56" s="23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J56" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="K56" s="22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="L56" s="22" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="M56" s="22" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="N56" s="22" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="B57" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G57" s="21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H57" s="21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I57" s="21" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J57" s="22" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="K57" s="22" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="L57" s="22" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="M57" s="22" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="N57" s="22" t="n">
+        <v>62.3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>Lambda</t>
+        </is>
+      </c>
+      <c r="B58" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G58" s="23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H58" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" s="23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J58" s="22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K58" s="22" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="L58" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="M58" s="22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="N58" s="22" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Crusoe Energy</t>
+        </is>
+      </c>
+      <c r="B59" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G59" s="21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H59" s="21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I59" s="21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J59" s="22" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K59" s="22" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="L59" s="22" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="M59" s="22" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="N59" s="22" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>Voltage Park</t>
+        </is>
+      </c>
+      <c r="B60" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H60" s="23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I60" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J60" s="22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K60" s="22" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="L60" s="22" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="M60" s="22" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="N60" s="22" t="n">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Together AI</t>
+        </is>
+      </c>
+      <c r="B61" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H61" s="21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I61" s="21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J61" s="22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K61" s="22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L61" s="22" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="M61" s="22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="N61" s="22" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>Applied Digital</t>
+        </is>
+      </c>
+      <c r="B62" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H62" s="23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I62" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J62" s="22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K62" s="22" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="L62" s="22" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="M62" s="22" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="N62" s="22" t="n">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>ROIC (%) — NOPAT / Average Invested Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="M65" s="4" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="N65" s="4" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Amazon (AWS)</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="13" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="D66" s="13" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="E66" s="13" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F66" s="13" t="n">
+        <v>0.0552</v>
+      </c>
+      <c r="G66" s="13" t="n">
+        <v>0.0728</v>
+      </c>
+      <c r="H66" s="13" t="n">
+        <v>0.0842</v>
+      </c>
+      <c r="I66" s="13" t="n">
+        <v>0.09379999999999999</v>
+      </c>
+      <c r="J66" s="14" t="n">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="K66" s="14" t="n">
+        <v>0.1049</v>
+      </c>
+      <c r="L66" s="14" t="n">
+        <v>0.1109</v>
+      </c>
+      <c r="M66" s="14" t="n">
+        <v>0.1195</v>
+      </c>
+      <c r="N66" s="14" t="n">
+        <v>0.1317</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>Microsoft (Azure)</t>
+        </is>
+      </c>
+      <c r="B67" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="17" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>0.0447</v>
+      </c>
+      <c r="F67" s="17" t="n">
+        <v>0.0828</v>
+      </c>
+      <c r="G67" s="17" t="n">
+        <v>0.1238</v>
+      </c>
+      <c r="H67" s="17" t="n">
+        <v>0.1644</v>
+      </c>
+      <c r="I67" s="17" t="n">
+        <v>0.1705</v>
+      </c>
+      <c r="J67" s="14" t="n">
+        <v>0.1713</v>
+      </c>
+      <c r="K67" s="14" t="n">
+        <v>0.1742</v>
+      </c>
+      <c r="L67" s="14" t="n">
+        <v>0.1833</v>
+      </c>
+      <c r="M67" s="14" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="N67" s="14" t="n">
+        <v>0.2109</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>Google (GCP)</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="13" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="E68" s="13" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="F68" s="13" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="G68" s="13" t="n">
+        <v>0.0404</v>
+      </c>
+      <c r="H68" s="13" t="n">
+        <v>0.0641</v>
+      </c>
+      <c r="I68" s="13" t="n">
+        <v>0.07829999999999999</v>
+      </c>
+      <c r="J68" s="14" t="n">
+        <v>0.0818</v>
+      </c>
+      <c r="K68" s="14" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="L68" s="14" t="n">
+        <v>0.0988</v>
+      </c>
+      <c r="M68" s="14" t="n">
+        <v>0.1077</v>
+      </c>
+      <c r="N68" s="14" t="n">
+        <v>0.1202</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B69" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="17" t="n">
+        <v>0.1263</v>
+      </c>
+      <c r="D69" s="17" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="E69" s="17" t="n">
+        <v>0.2542</v>
+      </c>
+      <c r="F69" s="17" t="n">
+        <v>0.2409</v>
+      </c>
+      <c r="G69" s="17" t="n">
+        <v>0.2384</v>
+      </c>
+      <c r="H69" s="17" t="n">
+        <v>0.2505</v>
+      </c>
+      <c r="I69" s="17" t="n">
+        <v>0.2415</v>
+      </c>
+      <c r="J69" s="14" t="n">
+        <v>0.2142</v>
+      </c>
+      <c r="K69" s="14" t="n">
+        <v>0.2051</v>
+      </c>
+      <c r="L69" s="14" t="n">
+        <v>0.2049</v>
+      </c>
+      <c r="M69" s="14" t="n">
+        <v>0.2124</v>
+      </c>
+      <c r="N69" s="14" t="n">
+        <v>0.2232</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>Oracle Cloud</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="13" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="G70" s="13" t="n">
+        <v>0.0407</v>
+      </c>
+      <c r="H70" s="13" t="n">
+        <v>0.08210000000000001</v>
+      </c>
+      <c r="I70" s="13" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="J70" s="14" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="K70" s="14" t="n">
+        <v>0.1276</v>
+      </c>
+      <c r="L70" s="14" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="M70" s="14" t="n">
+        <v>0.1459</v>
+      </c>
+      <c r="N70" s="14" t="n">
+        <v>0.1563</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="B71" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>0.0533</v>
+      </c>
+      <c r="F71" s="17" t="n">
+        <v>0.0615</v>
+      </c>
+      <c r="G71" s="17" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="H71" s="17" t="n">
+        <v>0.1711</v>
+      </c>
+      <c r="I71" s="17" t="n">
+        <v>0.2742</v>
+      </c>
+      <c r="J71" s="14" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="K71" s="14" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="L71" s="14" t="n">
+        <v>0.3713</v>
+      </c>
+      <c r="M71" s="14" t="n">
+        <v>0.4283</v>
+      </c>
+      <c r="N71" s="14" t="n">
+        <v>0.4886</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="B72" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="13" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="I72" s="13" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="J72" s="14" t="n">
+        <v>0.0318</v>
+      </c>
+      <c r="K72" s="14" t="n">
+        <v>0.0395</v>
+      </c>
+      <c r="L72" s="14" t="n">
+        <v>0.0473</v>
+      </c>
+      <c r="M72" s="14" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="N72" s="14" t="n">
+        <v>0.0596</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>Lambda</t>
+        </is>
+      </c>
+      <c r="B73" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="17" t="n">
+        <v>-0.0167</v>
+      </c>
+      <c r="I73" s="17" t="n">
+        <v>0.0158</v>
+      </c>
+      <c r="J73" s="14" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="K73" s="14" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="L73" s="14" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="M73" s="14" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="N73" s="14" t="n">
+        <v>0.043</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Crusoe Energy</t>
+        </is>
+      </c>
+      <c r="B74" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I74" s="13" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="J74" s="14" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="K74" s="14" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="L74" s="14" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="M74" s="14" t="n">
+        <v>0.0337</v>
+      </c>
+      <c r="N74" s="14" t="n">
+        <v>0.0385</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>Voltage Park</t>
+        </is>
+      </c>
+      <c r="B75" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="17" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="J75" s="14" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="K75" s="14" t="n">
+        <v>0.0218</v>
+      </c>
+      <c r="L75" s="14" t="n">
+        <v>0.0329</v>
+      </c>
+      <c r="M75" s="14" t="n">
+        <v>0.0402</v>
+      </c>
+      <c r="N75" s="14" t="n">
+        <v>0.0481</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Together AI</t>
+        </is>
+      </c>
+      <c r="B76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="13" t="n">
+        <v>-0.0133</v>
+      </c>
+      <c r="J76" s="14" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="K76" s="14" t="n">
+        <v>0.0229</v>
+      </c>
+      <c r="L76" s="14" t="n">
+        <v>0.0328</v>
+      </c>
+      <c r="M76" s="14" t="n">
+        <v>0.0426</v>
+      </c>
+      <c r="N76" s="14" t="n">
+        <v>0.0511</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>Applied Digital</t>
+        </is>
+      </c>
+      <c r="B77" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="17" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="J77" s="14" t="n">
+        <v>0.0262</v>
+      </c>
+      <c r="K77" s="14" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="L77" s="14" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="M77" s="14" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="N77" s="14" t="n">
+        <v>0.0576</v>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>Incremental ROIC (%) — ΔNOPATᵧ / ΔInvested Capitalᵧ₋₁ (Return on New Capital Deployed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="M80" s="4" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="N80" s="4" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Amazon (AWS)</t>
+        </is>
+      </c>
+      <c r="B81" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="13" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="D81" s="13" t="n">
+        <v>0.0187</v>
+      </c>
+      <c r="E81" s="13" t="n">
+        <v>0.0467</v>
+      </c>
+      <c r="F81" s="13" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="G81" s="13" t="n">
+        <v>0.0636</v>
+      </c>
+      <c r="H81" s="13" t="n">
+        <v>0.06469999999999999</v>
+      </c>
+      <c r="I81" s="13" t="n">
+        <v>0.0864</v>
+      </c>
+      <c r="J81" s="14" t="n">
+        <v>0.1049</v>
+      </c>
+      <c r="K81" s="14" t="n">
+        <v>0.1182</v>
+      </c>
+      <c r="L81" s="14" t="n">
+        <v>0.1327</v>
+      </c>
+      <c r="M81" s="14" t="n">
+        <v>0.1749</v>
+      </c>
+      <c r="N81" s="14" t="n">
+        <v>0.2449</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>Microsoft (Azure)</t>
+        </is>
+      </c>
+      <c r="B82" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="17" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F82" s="17" t="n">
+        <v>0.0791</v>
+      </c>
+      <c r="G82" s="17" t="n">
+        <v>0.1248</v>
+      </c>
+      <c r="H82" s="17" t="n">
+        <v>0.1412</v>
+      </c>
+      <c r="I82" s="17" t="n">
+        <v>0.1426</v>
+      </c>
+      <c r="J82" s="14" t="n">
+        <v>0.1656</v>
+      </c>
+      <c r="K82" s="14" t="n">
+        <v>0.1807</v>
+      </c>
+      <c r="L82" s="14" t="n">
+        <v>0.2217</v>
+      </c>
+      <c r="M82" s="14" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="N82" s="14" t="n">
+        <v>0.3827</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>Google (GCP)</t>
+        </is>
+      </c>
+      <c r="B83" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="13" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="E83" s="13" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="F83" s="13" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="G83" s="13" t="n">
+        <v>0.0441</v>
+      </c>
+      <c r="H83" s="13" t="n">
+        <v>0.0633</v>
+      </c>
+      <c r="I83" s="13" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="J83" s="14" t="n">
+        <v>0.0843</v>
+      </c>
+      <c r="K83" s="14" t="n">
+        <v>0.1113</v>
+      </c>
+      <c r="L83" s="14" t="n">
+        <v>0.1377</v>
+      </c>
+      <c r="M83" s="14" t="n">
+        <v>0.1683</v>
+      </c>
+      <c r="N83" s="14" t="n">
+        <v>0.2506</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B84" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="17" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="D84" s="17" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="E84" s="17" t="n">
+        <v>0.2159</v>
+      </c>
+      <c r="F84" s="17" t="n">
+        <v>0.1868</v>
+      </c>
+      <c r="G84" s="17" t="n">
+        <v>0.1697</v>
+      </c>
+      <c r="H84" s="17" t="n">
+        <v>0.2175</v>
+      </c>
+      <c r="I84" s="17" t="n">
+        <v>0.1824</v>
+      </c>
+      <c r="J84" s="14" t="n">
+        <v>0.1629</v>
+      </c>
+      <c r="K84" s="14" t="n">
+        <v>0.1886</v>
+      </c>
+      <c r="L84" s="14" t="n">
+        <v>0.2247</v>
+      </c>
+      <c r="M84" s="14" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="N84" s="14" t="n">
+        <v>0.4139</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>Oracle Cloud</t>
+        </is>
+      </c>
+      <c r="B85" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="13" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="G85" s="13" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="H85" s="13" t="n">
+        <v>0.0673</v>
+      </c>
+      <c r="I85" s="13" t="n">
+        <v>0.1087</v>
+      </c>
+      <c r="J85" s="14" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K85" s="14" t="n">
+        <v>0.1623</v>
+      </c>
+      <c r="L85" s="14" t="n">
+        <v>0.1824</v>
+      </c>
+      <c r="M85" s="14" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="N85" s="14" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="B86" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="17" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="G86" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H86" s="17" t="n">
+        <v>0.1889</v>
+      </c>
+      <c r="I86" s="17" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="J86" s="14" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="K86" s="14" t="n">
+        <v>0.3933</v>
+      </c>
+      <c r="L86" s="14" t="n">
+        <v>0.5512</v>
+      </c>
+      <c r="M86" s="14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N86" s="14" t="n">
+        <v>0.9935</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="B87" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="13" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="H87" s="13" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="I87" s="13" t="n">
+        <v>0.0239</v>
+      </c>
+      <c r="J87" s="14" t="n">
+        <v>0.0337</v>
+      </c>
+      <c r="K87" s="14" t="n">
+        <v>0.0482</v>
+      </c>
+      <c r="L87" s="14" t="n">
+        <v>0.0664</v>
+      </c>
+      <c r="M87" s="14" t="n">
+        <v>0.0827</v>
+      </c>
+      <c r="N87" s="14" t="n">
+        <v>0.0988</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>Lambda</t>
+        </is>
+      </c>
+      <c r="B88" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="17" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="J88" s="14" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="K88" s="14" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="L88" s="14" t="n">
+        <v>0.0419</v>
+      </c>
+      <c r="M88" s="14" t="n">
+        <v>0.0489</v>
+      </c>
+      <c r="N88" s="14" t="n">
+        <v>0.059</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>Crusoe Energy</t>
+        </is>
+      </c>
+      <c r="B89" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="13" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="I89" s="13" t="n">
+        <v>0.0136</v>
+      </c>
+      <c r="J89" s="14" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="K89" s="14" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="L89" s="14" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="M89" s="14" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="N89" s="14" t="n">
+        <v>0.0614</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>Voltage Park</t>
+        </is>
+      </c>
+      <c r="B90" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="17" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="J90" s="14" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="K90" s="14" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="L90" s="14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M90" s="14" t="n">
+        <v>0.0594</v>
+      </c>
+      <c r="N90" s="14" t="n">
+        <v>0.0828</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>Together AI</t>
+        </is>
+      </c>
+      <c r="B91" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="13" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="J91" s="14" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="K91" s="14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L91" s="14" t="n">
+        <v>0.0423</v>
+      </c>
+      <c r="M91" s="14" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="N91" s="14" t="n">
+        <v>0.07779999999999999</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>Applied Digital</t>
+        </is>
+      </c>
+      <c r="B92" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="17" t="n">
+        <v>0.0154</v>
+      </c>
+      <c r="J92" s="14" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="K92" s="14" t="n">
+        <v>0.0429</v>
+      </c>
+      <c r="L92" s="14" t="n">
+        <v>0.0531</v>
+      </c>
+      <c r="M92" s="14" t="n">
+        <v>0.0687</v>
+      </c>
+      <c r="N92" s="14" t="n">
+        <v>0.0897</v>
+      </c>
+    </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>ROIC Summary — Key Metrics by Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="28" customHeight="1">
+      <c r="A95" s="65" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B95" s="65" t="inlineStr">
+        <is>
+          <t>2024 ROIC</t>
+        </is>
+      </c>
+      <c r="C95" s="65" t="inlineStr">
+        <is>
+          <t>2025 ROIC</t>
+        </is>
+      </c>
+      <c r="D95" s="65" t="inlineStr">
+        <is>
+          <t>2026E ROIC</t>
+        </is>
+      </c>
+      <c r="E95" s="65" t="inlineStr">
+        <is>
+          <t>2028E ROIC</t>
+        </is>
+      </c>
+      <c r="F95" s="65" t="inlineStr">
+        <is>
+          <t>2030E ROIC</t>
+        </is>
+      </c>
+      <c r="G95" s="65" t="inlineStr">
+        <is>
+          <t>2025 NOPAT ($B)</t>
+        </is>
+      </c>
+      <c r="H95" s="65" t="inlineStr">
+        <is>
+          <t>2025 IC ($B)</t>
+        </is>
+      </c>
+      <c r="I95" s="65" t="inlineStr">
+        <is>
+          <t>Incr. ROIC 2025</t>
+        </is>
+      </c>
+      <c r="J95" s="65" t="inlineStr">
+        <is>
+          <t>Incr. ROIC 2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="50" t="inlineStr">
+        <is>
+          <t>Amazon (AWS)</t>
+        </is>
+      </c>
+      <c r="B96" s="41" t="n">
+        <v>0.0842</v>
+      </c>
+      <c r="C96" s="41" t="n">
+        <v>0.09379999999999999</v>
+      </c>
+      <c r="D96" s="41" t="n">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="E96" s="41" t="n">
+        <v>0.1109</v>
+      </c>
+      <c r="F96" s="41" t="n">
+        <v>0.1317</v>
+      </c>
+      <c r="G96" s="74" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H96" s="74" t="n">
+        <v>114.9</v>
+      </c>
+      <c r="I96" s="41" t="n">
+        <v>0.0864</v>
+      </c>
+      <c r="J96" s="41" t="n">
+        <v>0.2449</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="51" t="inlineStr">
+        <is>
+          <t>Microsoft (Azure)</t>
+        </is>
+      </c>
+      <c r="B97" s="46" t="n">
+        <v>0.1644</v>
+      </c>
+      <c r="C97" s="46" t="n">
+        <v>0.1705</v>
+      </c>
+      <c r="D97" s="46" t="n">
+        <v>0.1713</v>
+      </c>
+      <c r="E97" s="46" t="n">
+        <v>0.1833</v>
+      </c>
+      <c r="F97" s="46" t="n">
+        <v>0.2109</v>
+      </c>
+      <c r="G97" s="75" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H97" s="75" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="I97" s="46" t="n">
+        <v>0.1426</v>
+      </c>
+      <c r="J97" s="46" t="n">
+        <v>0.3827</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="50" t="inlineStr">
+        <is>
+          <t>Google (GCP)</t>
+        </is>
+      </c>
+      <c r="B98" s="41" t="n">
+        <v>0.0641</v>
+      </c>
+      <c r="C98" s="41" t="n">
+        <v>0.07829999999999999</v>
+      </c>
+      <c r="D98" s="41" t="n">
+        <v>0.0818</v>
+      </c>
+      <c r="E98" s="41" t="n">
+        <v>0.0988</v>
+      </c>
+      <c r="F98" s="41" t="n">
+        <v>0.1202</v>
+      </c>
+      <c r="G98" s="74" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H98" s="74" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="I98" s="41" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="J98" s="41" t="n">
+        <v>0.2506</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="51" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B99" s="46" t="n">
+        <v>0.2505</v>
+      </c>
+      <c r="C99" s="46" t="n">
+        <v>0.2415</v>
+      </c>
+      <c r="D99" s="46" t="n">
+        <v>0.2142</v>
+      </c>
+      <c r="E99" s="46" t="n">
+        <v>0.2049</v>
+      </c>
+      <c r="F99" s="46" t="n">
+        <v>0.2232</v>
+      </c>
+      <c r="G99" s="75" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H99" s="75" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="I99" s="46" t="n">
+        <v>0.1824</v>
+      </c>
+      <c r="J99" s="46" t="n">
+        <v>0.4139</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="50" t="inlineStr">
+        <is>
+          <t>Oracle Cloud</t>
+        </is>
+      </c>
+      <c r="B100" s="41" t="n">
+        <v>0.08210000000000001</v>
+      </c>
+      <c r="C100" s="41" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="D100" s="41" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="E100" s="41" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="F100" s="41" t="n">
+        <v>0.1563</v>
+      </c>
+      <c r="G100" s="74" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H100" s="74" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="I100" s="41" t="n">
+        <v>0.1087</v>
+      </c>
+      <c r="J100" s="41" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="51" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="B101" s="46" t="n">
+        <v>0.1711</v>
+      </c>
+      <c r="C101" s="46" t="n">
+        <v>0.2742</v>
+      </c>
+      <c r="D101" s="46" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="E101" s="46" t="n">
+        <v>0.3713</v>
+      </c>
+      <c r="F101" s="46" t="n">
+        <v>0.4886</v>
+      </c>
+      <c r="G101" s="75" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H101" s="75" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I101" s="46" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="J101" s="46" t="n">
+        <v>0.9935</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="50" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="B102" s="41" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="C102" s="41" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="D102" s="41" t="n">
+        <v>0.0318</v>
+      </c>
+      <c r="E102" s="41" t="n">
+        <v>0.0473</v>
+      </c>
+      <c r="F102" s="41" t="n">
+        <v>0.0596</v>
+      </c>
+      <c r="G102" s="74" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H102" s="74" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="I102" s="41" t="n">
+        <v>0.0239</v>
+      </c>
+      <c r="J102" s="41" t="n">
+        <v>0.0988</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="51" t="inlineStr">
+        <is>
+          <t>Lambda</t>
+        </is>
+      </c>
+      <c r="B103" s="46" t="n">
+        <v>-0.0167</v>
+      </c>
+      <c r="C103" s="46" t="n">
+        <v>0.0158</v>
+      </c>
+      <c r="D103" s="46" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="E103" s="46" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="F103" s="46" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="G103" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="75" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I103" s="46" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="J103" s="46" t="n">
+        <v>0.059</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="50" t="inlineStr">
+        <is>
+          <t>Crusoe Energy</t>
+        </is>
+      </c>
+      <c r="B104" s="41" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C104" s="41" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="D104" s="41" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="E104" s="41" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="F104" s="41" t="n">
+        <v>0.0385</v>
+      </c>
+      <c r="G104" s="74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="74" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I104" s="41" t="n">
+        <v>0.0136</v>
+      </c>
+      <c r="J104" s="41" t="n">
+        <v>0.0614</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="51" t="inlineStr">
+        <is>
+          <t>Voltage Park</t>
+        </is>
+      </c>
+      <c r="B105" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="46" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="D105" s="46" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="E105" s="46" t="n">
+        <v>0.0329</v>
+      </c>
+      <c r="F105" s="46" t="n">
+        <v>0.0481</v>
+      </c>
+      <c r="G105" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="75" t="n">
+        <v>2</v>
+      </c>
+      <c r="I105" s="46" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="J105" s="46" t="n">
+        <v>0.0828</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="50" t="inlineStr">
+        <is>
+          <t>Together AI</t>
+        </is>
+      </c>
+      <c r="B106" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C106" s="41" t="n">
+        <v>-0.0133</v>
+      </c>
+      <c r="D106" s="41" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="E106" s="41" t="n">
+        <v>0.0328</v>
+      </c>
+      <c r="F106" s="41" t="n">
+        <v>0.0511</v>
+      </c>
+      <c r="G106" s="74" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H106" s="74" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I106" s="41" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="J106" s="41" t="n">
+        <v>0.07779999999999999</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="51" t="inlineStr">
+        <is>
+          <t>Applied Digital</t>
+        </is>
+      </c>
+      <c r="B107" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="46" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="D107" s="46" t="n">
+        <v>0.0262</v>
+      </c>
+      <c r="E107" s="46" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="F107" s="46" t="n">
+        <v>0.0576</v>
+      </c>
+      <c r="G107" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="75" t="n">
+        <v>2</v>
+      </c>
+      <c r="I107" s="46" t="n">
+        <v>0.0154</v>
+      </c>
+      <c r="J107" s="46" t="n">
+        <v>0.0897</v>
+      </c>
+    </row>
+    <row r="110" ht="22" customHeight="1">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>Key ROIC Observations</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="30" customHeight="1">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B111" s="72" t="inlineStr">
+        <is>
+          <t>MICROSOFT leads in ROIC among hyperscalers: strong Copilot/OpenAI monetization + high margin (36-44%) on AI cloud revenue yields the highest return on AI invested capital; ROIC crosses 20%+ by 2027-2028E</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="30" customHeight="1">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B112" s="72" t="inlineStr">
+        <is>
+          <t>META has the highest absolute ROIC due to its unique model: AI capex improves ad targeting with very high incremental margins (44-48%); internal AI deployments have minimal sales/GTM cost vs external cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="30" customHeight="1">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B113" s="72" t="inlineStr">
+        <is>
+          <t>AMAZON (AWS) shows improving ROIC trajectory: AI margins expanding from 26% (2024) to 38% (2030E) as Bedrock/Trainium/Inferentia scale; ROIC inflects positive by 2024-2025 and improves steadily</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="30" customHeight="1">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B114" s="72" t="inlineStr">
+        <is>
+          <t>ORACLE has the fastest ROIC improvement rate: starting from near-zero in 2023, expanding rapidly as OCI AI contracts scale against a still-modest capital base; by 2030E ROIC approaches 20-25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="30" customHeight="1">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B115" s="72" t="inlineStr">
+        <is>
+          <t>NEOCLOUDS show low but improving ROIC: heavy capex front-loading (GPU fleet) with thin margins initially; CoreWeave and Lambda achieving positive NOPAT by 2025; ROIC expected at 5-10% by 2028-2030E as margins normalize</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="30" customHeight="1">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B116" s="72" t="inlineStr">
+        <is>
+          <t>INCREMENTAL ROIC is the key forward-looking metric: shows the return on the NEXT dollar invested; hyperscalers showing 15-25%+ incremental ROIC by 2027-2030E, validating continued AI capex acceleration</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="30" customHeight="1">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B117" s="72" t="inlineStr">
+        <is>
+          <t>APPLE stands out with very high ROIC due to low AI capex relative to the massive services revenue uplift enabled by Apple Intelligence; atypical model vs pure cloud providers</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="30" customHeight="1">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B118" s="72" t="inlineStr">
+        <is>
+          <t>Key assumption: invested capital uses 7-year blended depreciation life (servers 4-5yr, buildings 15-20yr); different depreciation assumptions materially affect ROIC levels</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A94:N94"/>
+    <mergeCell ref="A110:N110"/>
+    <mergeCell ref="A79:N79"/>
+    <mergeCell ref="B115:N115"/>
+    <mergeCell ref="B114:N114"/>
+    <mergeCell ref="A34:N34"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="B118:N118"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="B113:N113"/>
+    <mergeCell ref="A64:N64"/>
+    <mergeCell ref="B112:N112"/>
+    <mergeCell ref="A19:N19"/>
+    <mergeCell ref="A49:N49"/>
+    <mergeCell ref="B116:N116"/>
+    <mergeCell ref="B117:N117"/>
+    <mergeCell ref="B111:N111"/>
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00999999"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -30625,7 +36613,7 @@
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="74" t="inlineStr">
+      <c r="A3" s="76" t="inlineStr">
         <is>
           <t>Data Sources</t>
         </is>
@@ -30637,7 +36625,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B4" s="75" t="inlineStr">
+      <c r="B4" s="77" t="inlineStr">
         <is>
           <t>2024-2025 capex and revenue actuals from 10-K filings and 4Q25 earnings calls (Jan/Feb 2026)</t>
         </is>
@@ -30649,7 +36637,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B5" s="75" t="inlineStr">
+      <c r="B5" s="77" t="inlineStr">
         <is>
           <t>2026E capex from explicit guidance on 4Q25 earnings calls (Amazon, Microsoft, Google, Meta, Oracle, Apple)</t>
         </is>
@@ -30661,7 +36649,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B6" s="75" t="inlineStr">
+      <c r="B6" s="77" t="inlineStr">
         <is>
           <t>Historical capex and revenue from public SEC filings (10-K, 10-Q) and earnings calls</t>
         </is>
@@ -30673,7 +36661,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B7" s="75" t="inlineStr">
+      <c r="B7" s="77" t="inlineStr">
         <is>
           <t>Server counts estimated from industry reports (Synergy Research, Dell'Oro, Omdia)</t>
         </is>
@@ -30685,7 +36673,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B8" s="75" t="inlineStr">
+      <c r="B8" s="77" t="inlineStr">
         <is>
           <t>Datacenter counts from company announcements, press releases, and analyst estimates</t>
         </is>
@@ -30697,7 +36685,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B9" s="75" t="inlineStr">
+      <c r="B9" s="77" t="inlineStr">
         <is>
           <t>Power capacity from sustainability reports, PPA announcements, and utility filings</t>
         </is>
@@ -30709,7 +36697,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B10" s="75" t="inlineStr">
+      <c r="B10" s="77" t="inlineStr">
         <is>
           <t>Neocloud data from funding announcements, press coverage, and industry estimates</t>
         </is>
@@ -30721,7 +36709,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B11" s="75" t="inlineStr">
+      <c r="B11" s="77" t="inlineStr">
         <is>
           <t>Colo/REIT data from NAREIT filings, investor presentations, and quarterly supplements</t>
         </is>
@@ -30733,7 +36721,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B12" s="75" t="inlineStr">
+      <c r="B12" s="77" t="inlineStr">
         <is>
           <t>Power supply data from EIA, FERC, ISO/RTO reports, and utility IRP filings</t>
         </is>
@@ -30745,7 +36733,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B13" s="75" t="inlineStr">
+      <c r="B13" s="77" t="inlineStr">
         <is>
           <t>BOM costs from construction industry benchmarks, vendor quotes, and DC operator disclosures</t>
         </is>
@@ -30757,14 +36745,14 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B14" s="75" t="inlineStr">
+      <c r="B14" s="77" t="inlineStr">
         <is>
           <t>Supply chain TAM from Gartner, IDC, Dell'Oro, and company-reported revenue segmentation</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="74" t="inlineStr">
+      <c r="A16" s="76" t="inlineStr">
         <is>
           <t>Key Assumptions — Forecasts (2025E-2030E)</t>
         </is>
@@ -30776,7 +36764,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B17" s="75" t="inlineStr">
+      <c r="B17" s="77" t="inlineStr">
         <is>
           <t>AI infrastructure buildout continues to accelerate through 2027, moderating thereafter</t>
         </is>
@@ -30788,7 +36776,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B18" s="75" t="inlineStr">
+      <c r="B18" s="77" t="inlineStr">
         <is>
           <t>Hyperscaler capex growth driven by AI/ML workloads, sovereign cloud, and edge expansion</t>
         </is>
@@ -30800,7 +36788,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B19" s="75" t="inlineStr">
+      <c r="B19" s="77" t="inlineStr">
         <is>
           <t>Neocloud vendors benefit from GPU-as-a-service demand but face capital constraints</t>
         </is>
@@ -30812,7 +36800,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B20" s="75" t="inlineStr">
+      <c r="B20" s="77" t="inlineStr">
         <is>
           <t>Colo/REIT capex accelerates as hyperscalers increasingly lease rather than build</t>
         </is>
@@ -30824,7 +36812,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B21" s="75" t="inlineStr">
+      <c r="B21" s="77" t="inlineStr">
         <is>
           <t>Power availability is the key constraint on datacenter buildout after 2026</t>
         </is>
@@ -30836,7 +36824,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B22" s="75" t="inlineStr">
+      <c r="B22" s="77" t="inlineStr">
         <is>
           <t>Renewable energy targets: most hyperscalers reach 100% by 2027-2030</t>
         </is>
@@ -30848,7 +36836,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B23" s="75" t="inlineStr">
+      <c r="B23" s="77" t="inlineStr">
         <is>
           <t>Server density improves 8-12% annually (more compute per rack unit)</t>
         </is>
@@ -30860,7 +36848,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B24" s="75" t="inlineStr">
+      <c r="B24" s="77" t="inlineStr">
         <is>
           <t>Average PUE improves from ~1.3 (2024) to ~1.15 (2030) industry-wide</t>
         </is>
@@ -30872,7 +36860,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B25" s="75" t="inlineStr">
+      <c r="B25" s="77" t="inlineStr">
         <is>
           <t>SMR/advanced nuclear begins contributing meaningfully after 2028</t>
         </is>
@@ -30884,14 +36872,14 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B26" s="75" t="inlineStr">
+      <c r="B26" s="77" t="inlineStr">
         <is>
           <t>Transformer lead times peak in 2025-2026, gradually improve as manufacturing scales</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="74" t="inlineStr">
+      <c r="A28" s="76" t="inlineStr">
         <is>
           <t>Power Supply Assumptions</t>
         </is>
@@ -30903,7 +36891,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B29" s="75" t="inlineStr">
+      <c r="B29" s="77" t="inlineStr">
         <is>
           <t>Natural gas remains the primary source for near-term DC power additions through 2027</t>
         </is>
@@ -30915,7 +36903,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B30" s="75" t="inlineStr">
+      <c r="B30" s="77" t="inlineStr">
         <is>
           <t>Solar + battery storage combinations become cost-competitive for 24/7 DC power by 2028</t>
         </is>
@@ -30927,7 +36915,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B31" s="75" t="inlineStr">
+      <c r="B31" s="77" t="inlineStr">
         <is>
           <t>Nuclear (SMR) first commercial deployments for DC use begin in 2027-2028</t>
         </is>
@@ -30939,7 +36927,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B32" s="75" t="inlineStr">
+      <c r="B32" s="77" t="inlineStr">
         <is>
           <t>Grid interconnection queue times peak at ~42 months in 2025E, declining as processes streamline</t>
         </is>
@@ -30951,7 +36939,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B33" s="75" t="inlineStr">
+      <c r="B33" s="77" t="inlineStr">
         <is>
           <t>Average DC power cost peaks at ~$72/MWh in 2025E before declining with renewables scale</t>
         </is>
@@ -30963,14 +36951,14 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B34" s="75" t="inlineStr">
+      <c r="B34" s="77" t="inlineStr">
         <is>
           <t>Behind-the-meter generation (on-site solar, fuel cells) grows from &lt;5% to ~15% by 2030</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="74" t="inlineStr">
+      <c r="A36" s="76" t="inlineStr">
         <is>
           <t>Bill of Materials Assumptions</t>
         </is>
@@ -30982,7 +36970,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B37" s="75" t="inlineStr">
+      <c r="B37" s="77" t="inlineStr">
         <is>
           <t>BOM costs reflect average hyperscale build; enterprise/colo builds may differ by 20-30%</t>
         </is>
@@ -30994,7 +36982,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B38" s="75" t="inlineStr">
+      <c r="B38" s="77" t="inlineStr">
         <is>
           <t>GPU server costs assume mix of NVIDIA H100/B200/next-gen accelerators at typical deployment ratios</t>
         </is>
@@ -31006,7 +36994,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B39" s="75" t="inlineStr">
+      <c r="B39" s="77" t="inlineStr">
         <is>
           <t>Liquid cooling penetration grows from ~10% of new builds (2024) to ~60% (2030E) for AI-heavy facilities</t>
         </is>
@@ -31018,7 +37006,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B40" s="75" t="inlineStr">
+      <c r="B40" s="77" t="inlineStr">
         <is>
           <t>Electrical infrastructure costs include transformer premiums from current supply shortage</t>
         </is>
@@ -31030,14 +37018,14 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B41" s="75" t="inlineStr">
+      <c r="B41" s="77" t="inlineStr">
         <is>
           <t>Construction labor cost inflation of ~3-5% annually, partially offset by modular/prefab methods</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="74" t="inlineStr">
+      <c r="A43" s="76" t="inlineStr">
         <is>
           <t>Supply Chain Assumptions</t>
         </is>
@@ -31049,7 +37037,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B44" s="75" t="inlineStr">
+      <c r="B44" s="77" t="inlineStr">
         <is>
           <t>TAM figures represent addressable market for DC-specific spend (not total vendor revenue)</t>
         </is>
@@ -31061,7 +37049,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B45" s="75" t="inlineStr">
+      <c r="B45" s="77" t="inlineStr">
         <is>
           <t>Servers &amp; GPUs segment is the largest and fastest-growing, driven by AI accelerator demand</t>
         </is>
@@ -31073,7 +37061,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B46" s="75" t="inlineStr">
+      <c r="B46" s="77" t="inlineStr">
         <is>
           <t>Supply chain TAM exceeds operator capex because it includes maintenance, refresh, and software</t>
         </is>
@@ -31085,7 +37073,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B47" s="75" t="inlineStr">
+      <c r="B47" s="77" t="inlineStr">
         <is>
           <t>Revenue multiplier (TAM/Capex) reflects that capex flows through multiple vendor layers</t>
         </is>
@@ -31097,16 +37085,16 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B48" s="75" t="inlineStr">
+      <c r="B48" s="77" t="inlineStr">
         <is>
           <t>Key supply chain bottlenecks: GPU supply, transformer manufacturing, skilled labor, power</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="74" t="inlineStr">
-        <is>
-          <t>Capex Decomposition Assumptions</t>
+      <c r="A50" s="76" t="inlineStr">
+        <is>
+          <t>ROIC Analysis Assumptions</t>
         </is>
       </c>
     </row>
@@ -31116,9 +37104,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B51" s="75" t="inlineStr">
-        <is>
-          <t>Component price indices use 2020 as base year (index = 100); chosen because 2020 was pre-inflation, pre-AI-boom baseline</t>
+      <c r="B51" s="77" t="inlineStr">
+        <is>
+          <t>ROIC = NOPAT / Average Invested Capital; measures the after-tax return generated per dollar of capital invested in AI infrastructure</t>
         </is>
       </c>
     </row>
@@ -31128,9 +37116,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B52" s="75" t="inlineStr">
-        <is>
-          <t>GPU/AI Accelerator index reflects weighted-average price of datacenter GPUs (H100, A100, B200 equivalent); rose sharply 2021-2024 on NVIDIA pricing power, now moderating with AMD competition and next-gen efficiency</t>
+      <c r="B52" s="77" t="inlineStr">
+        <is>
+          <t>Revenue base: AI-specific revenue for hyperscalers (cloud AI services, Copilot, etc.); total revenue for neoclouds (which is ~100% AI/GPU-as-a-service)</t>
         </is>
       </c>
     </row>
@@ -31140,9 +37128,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B53" s="75" t="inlineStr">
-        <is>
-          <t>HV Transformer index reflects 85-95% price premium vs 2020 driven by 36+ month lead times; new manufacturing capacity (Hitachi, Siemens, ABB) gradually easing supply by 2027-2028</t>
+      <c r="B53" s="77" t="inlineStr">
+        <is>
+          <t>Operating margins estimated from segment-level disclosures where available (AWS, Azure, GCP); otherwise based on peer margins and management commentary</t>
         </is>
       </c>
     </row>
@@ -31152,9 +37140,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B54" s="75" t="inlineStr">
-        <is>
-          <t>Weighted-average index uses 2024 BOM cost shares as weights: GPU/AI 30%, CPU 12%, construction 10%, networking 9%, transformers 7%, land 6%, etc.</t>
+      <c r="B54" s="77" t="inlineStr">
+        <is>
+          <t>Meta margin reflects AI-attributable ad revenue uplift — high margin because AI improves existing ad platform vs building new service from scratch</t>
         </is>
       </c>
     </row>
@@ -31164,9 +37152,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B55" s="75" t="inlineStr">
-        <is>
-          <t>Capex decomposition uses formula: Total Capex = (New GW x Base $/MW) + (New GW x Inflation $/MW) + Other/Maintenance</t>
+      <c r="B55" s="77" t="inlineStr">
+        <is>
+          <t>Neocloud margins start negative (heavy COGS from GPU depreciation + power costs) and improve toward 20-25% at scale as utilization rises</t>
         </is>
       </c>
     </row>
@@ -31176,9 +37164,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B56" s="75" t="inlineStr">
-        <is>
-          <t>Base $/MW is frozen at each company's 2020 cost per MW of new capacity; inflation $/MW = current cost/MW minus base</t>
+      <c r="B56" s="77" t="inlineStr">
+        <is>
+          <t>Tax rate: 21% effective (US federal corporate rate); does not account for R&amp;D credits, international structures, or NOL carryforwards</t>
         </is>
       </c>
     </row>
@@ -31188,9 +37176,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B57" s="75" t="inlineStr">
-        <is>
-          <t>'Other/Maintenance' includes sustaining capex on existing facilities, non-capacity investments, and any residual not captured by the volume x price model</t>
+      <c r="B57" s="77" t="inlineStr">
+        <is>
+          <t>Invested capital: cumulative AI capex less accumulated straight-line depreciation at 7-year blended useful life</t>
         </is>
       </c>
     </row>
@@ -31200,9 +37188,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B58" s="75" t="inlineStr">
-        <is>
-          <t>Liquid cooling is the only major component with sustained deflation — prices falling ~15-20% annually as technology matures from niche to standard</t>
+      <c r="B58" s="77" t="inlineStr">
+        <is>
+          <t>7-year useful life is blended average: GPU servers 4-5 years, power/cooling infrastructure 12-15 years, buildings 20+ years</t>
         </is>
       </c>
     </row>
@@ -31212,28 +37200,28 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B59" s="75" t="inlineStr">
-        <is>
-          <t>Peak industry-wide component inflation was 2024-2025; moderating through 2030 but not returning to 2020 levels (structural premiums in land, labor, GPUs remain)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="74" t="inlineStr">
-        <is>
-          <t>AI Capex-to-Revenue Assumptions</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="B59" s="77" t="inlineStr">
+        <is>
+          <t>Incremental ROIC = change in NOPAT / change in invested capital; captures the marginal return on each new dollar invested</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B62" s="75" t="inlineStr">
-        <is>
-          <t>AI Capex = portion of total capex allocated to GPU clusters, AI networking, liquid cooling for AI, AI-dedicated DCs</t>
+      <c r="B60" s="77" t="inlineStr">
+        <is>
+          <t>ROIC levels are sensitive to depreciation assumptions; shorter useful life → lower IC → higher ROIC (and vice versa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="76" t="inlineStr">
+        <is>
+          <t>Capex Decomposition Assumptions</t>
         </is>
       </c>
     </row>
@@ -31243,9 +37231,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B63" s="75" t="inlineStr">
-        <is>
-          <t>AI Revenue = revenue directly attributable to AI: cloud AI services (hyperscalers), GPU-as-a-service (neoclouds), AI tenant leases (colo/REITs)</t>
+      <c r="B63" s="77" t="inlineStr">
+        <is>
+          <t>Component price indices use 2020 as base year (index = 100); chosen because 2020 was pre-inflation, pre-AI-boom baseline</t>
         </is>
       </c>
     </row>
@@ -31255,9 +37243,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B64" s="75" t="inlineStr">
-        <is>
-          <t>Meta AI revenue represents estimated uplift to advertising revenue from AI-powered recommendation and targeting improvements</t>
+      <c r="B64" s="77" t="inlineStr">
+        <is>
+          <t>GPU/AI Accelerator index reflects weighted-average price of datacenter GPUs (H100, A100, B200 equivalent); rose sharply 2021-2024 on NVIDIA pricing power, now moderating with AMD competition and next-gen efficiency</t>
         </is>
       </c>
     </row>
@@ -31267,9 +37255,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B65" s="75" t="inlineStr">
-        <is>
-          <t>Apple AI revenue reflects Apple Intelligence services, Siri improvements, and AI-enhanced services revenue uplift</t>
+      <c r="B65" s="77" t="inlineStr">
+        <is>
+          <t>HV Transformer index reflects 85-95% price premium vs 2020 driven by 36+ month lead times; new manufacturing capacity (Hitachi, Siemens, ABB) gradually easing supply by 2027-2028</t>
         </is>
       </c>
     </row>
@@ -31279,9 +37267,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B66" s="75" t="inlineStr">
-        <is>
-          <t>Oracle AI revenue driven by OCI GPU superclusters, Autonomous Database AI features, and AI cloud infrastructure</t>
+      <c r="B66" s="77" t="inlineStr">
+        <is>
+          <t>Weighted-average index uses 2024 BOM cost shares as weights: GPU/AI 30%, CPU 12%, construction 10%, networking 9%, transformers 7%, land 6%, etc.</t>
         </is>
       </c>
     </row>
@@ -31291,9 +37279,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B67" s="75" t="inlineStr">
-        <is>
-          <t>Capex-to-revenue lag varies by business model: neoclouds ~4 qtrs (direct GPU lease), hyperscalers ~5-8 qtrs (build→GA→ramp), colo ~6-7 qtrs (lease negotiation)</t>
+      <c r="B67" s="77" t="inlineStr">
+        <is>
+          <t>Capex decomposition uses formula: Total Capex = (New GW x Base $/MW) + (New GW x Inflation $/MW) + Other/Maintenance</t>
         </is>
       </c>
     </row>
@@ -31303,9 +37291,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B68" s="75" t="inlineStr">
-        <is>
-          <t>Cumulative payback year = first year where cumulative AI revenue &gt;= cumulative AI capex since inception</t>
+      <c r="B68" s="77" t="inlineStr">
+        <is>
+          <t>Base $/MW is frozen at each company's 2020 cost per MW of new capacity; inflation $/MW = current cost/MW minus base</t>
         </is>
       </c>
     </row>
@@ -31315,9 +37303,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B69" s="75" t="inlineStr">
-        <is>
-          <t>Annual AI Rev/Capex ratio &gt;1.0x indicates that year's AI revenue exceeds that year's AI capex investment</t>
+      <c r="B69" s="77" t="inlineStr">
+        <is>
+          <t>'Other/Maintenance' includes sustaining capex on existing facilities, non-capacity investments, and any residual not captured by the volume x price model</t>
         </is>
       </c>
     </row>
@@ -31327,28 +37315,28 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B70" s="75" t="inlineStr">
-        <is>
-          <t>Payback analysis does not account for depreciation, opex, or cost of capital; represents gross capex recovery only</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="22" customHeight="1">
-      <c r="A72" s="74" t="inlineStr">
-        <is>
-          <t>Colocation / REIT Assumptions</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="B70" s="77" t="inlineStr">
+        <is>
+          <t>Liquid cooling is the only major component with sustained deflation — prices falling ~15-20% annually as technology matures from niche to standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B73" s="75" t="inlineStr">
-        <is>
-          <t>Equinix, Digital Realty data from public REIT filings and investor supplements</t>
+      <c r="B71" s="77" t="inlineStr">
+        <is>
+          <t>Peak industry-wide component inflation was 2024-2025; moderating through 2030 but not returning to 2020 levels (structural premiums in land, labor, GPUs remain)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="76" t="inlineStr">
+        <is>
+          <t>AI Capex-to-Revenue Assumptions</t>
         </is>
       </c>
     </row>
@@ -31358,9 +37346,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B74" s="75" t="inlineStr">
-        <is>
-          <t>CyrusOne (KKR/GIP) and QTS (Blackstone) data estimated post-acquisition from industry reports</t>
+      <c r="B74" s="77" t="inlineStr">
+        <is>
+          <t>AI Capex = portion of total capex allocated to GPU clusters, AI networking, liquid cooling for AI, AI-dedicated DCs</t>
         </is>
       </c>
     </row>
@@ -31370,9 +37358,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B75" s="75" t="inlineStr">
-        <is>
-          <t>Vantage and Switch data from press releases, funding announcements, and analyst estimates</t>
+      <c r="B75" s="77" t="inlineStr">
+        <is>
+          <t>AI Revenue = revenue directly attributable to AI: cloud AI services (hyperscalers), GPU-as-a-service (neoclouds), AI tenant leases (colo/REITs)</t>
         </is>
       </c>
     </row>
@@ -31382,9 +37370,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B76" s="75" t="inlineStr">
-        <is>
-          <t>Colo revenue is facility/leasing revenue; does not include cloud service revenue</t>
+      <c r="B76" s="77" t="inlineStr">
+        <is>
+          <t>Meta AI revenue represents estimated uplift to advertising revenue from AI-powered recommendation and targeting improvements</t>
         </is>
       </c>
     </row>
@@ -31394,9 +37382,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B77" s="75" t="inlineStr">
-        <is>
-          <t>DC counts for Colo/REITs include all owned and operated facilities globally</t>
+      <c r="B77" s="77" t="inlineStr">
+        <is>
+          <t>Apple AI revenue reflects Apple Intelligence services, Siri improvements, and AI-enhanced services revenue uplift</t>
         </is>
       </c>
     </row>
@@ -31406,16 +37394,33 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B78" s="75" t="inlineStr">
-        <is>
-          <t>Server counts for Colo/REITs represent customer-deployed servers hosted in their facilities</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="22" customHeight="1">
-      <c r="A80" s="74" t="inlineStr">
-        <is>
-          <t>Definitions</t>
+      <c r="B78" s="77" t="inlineStr">
+        <is>
+          <t>Oracle AI revenue driven by OCI GPU superclusters, Autonomous Database AI features, and AI cloud infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B79" s="77" t="inlineStr">
+        <is>
+          <t>Capex-to-revenue lag varies by business model: neoclouds ~4 qtrs (direct GPU lease), hyperscalers ~5-8 qtrs (build→GA→ramp), colo ~6-7 qtrs (lease negotiation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B80" s="77" t="inlineStr">
+        <is>
+          <t>Cumulative payback year = first year where cumulative AI revenue &gt;= cumulative AI capex since inception</t>
         </is>
       </c>
     </row>
@@ -31425,9 +37430,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B81" s="75" t="inlineStr">
-        <is>
-          <t>IT Load (GW): Total electrical power consumed by IT equipment (servers, storage, networking)</t>
+      <c r="B81" s="77" t="inlineStr">
+        <is>
+          <t>Annual AI Rev/Capex ratio &gt;1.0x indicates that year's AI revenue exceeds that year's AI capex investment</t>
         </is>
       </c>
     </row>
@@ -31437,33 +37442,16 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B82" s="75" t="inlineStr">
-        <is>
-          <t>Power Contracted (GW): Total power capacity secured via PPAs, utility contracts, and on-site generation</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B83" s="75" t="inlineStr">
-        <is>
-          <t>Power Utilization: IT Load / Power Contracted (higher = more efficient use of secured power)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B84" s="75" t="inlineStr">
-        <is>
-          <t>Revenue/MW: Annual revenue ($B) / IT Load (GW); result is in $M/MW (since 1 GW = 1000 MW)</t>
+      <c r="B82" s="77" t="inlineStr">
+        <is>
+          <t>Payback analysis does not account for depreciation, opex, or cost of capital; represents gross capex recovery only</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="76" t="inlineStr">
+        <is>
+          <t>Colocation / REIT Assumptions</t>
         </is>
       </c>
     </row>
@@ -31473,9 +37461,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B85" s="75" t="inlineStr">
-        <is>
-          <t>Capex/MW: Annual capex ($B) / IT Load (GW) — investment intensity per MW of IT capacity</t>
+      <c r="B85" s="77" t="inlineStr">
+        <is>
+          <t>Equinix, Digital Realty data from public REIT filings and investor supplements</t>
         </is>
       </c>
     </row>
@@ -31485,9 +37473,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B86" s="75" t="inlineStr">
-        <is>
-          <t>Servers (000s): Total server count in thousands across all datacenter locations</t>
+      <c r="B86" s="77" t="inlineStr">
+        <is>
+          <t>CyrusOne (KKR/GIP) and QTS (Blackstone) data estimated post-acquisition from industry reports</t>
         </is>
       </c>
     </row>
@@ -31497,9 +37485,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B87" s="75" t="inlineStr">
-        <is>
-          <t>TAM: Total Addressable Market — revenue opportunity for vendors in each supply chain segment</t>
+      <c r="B87" s="77" t="inlineStr">
+        <is>
+          <t>Vantage and Switch data from press releases, funding announcements, and analyst estimates</t>
         </is>
       </c>
     </row>
@@ -31509,9 +37497,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B88" s="75" t="inlineStr">
-        <is>
-          <t>BOM: Bill of Materials — component and construction cost breakdown per MW of IT load</t>
+      <c r="B88" s="77" t="inlineStr">
+        <is>
+          <t>Colo revenue is facility/leasing revenue; does not include cloud service revenue</t>
         </is>
       </c>
     </row>
@@ -31521,9 +37509,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B89" s="75" t="inlineStr">
-        <is>
-          <t>AI Capex: Portion of total capex allocated specifically to AI/ML infrastructure (GPU clusters, AI networking, liquid cooling)</t>
+      <c r="B89" s="77" t="inlineStr">
+        <is>
+          <t>DC counts for Colo/REITs include all owned and operated facilities globally</t>
         </is>
       </c>
     </row>
@@ -31533,40 +37521,40 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B90" s="75" t="inlineStr">
-        <is>
-          <t>AI Revenue: Revenue directly attributable to AI products and services (cloud AI, GPU-as-a-service, AI tenant leases)</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="B90" s="77" t="inlineStr">
+        <is>
+          <t>Server counts for Colo/REITs represent customer-deployed servers hosted in their facilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="22" customHeight="1">
+      <c r="A92" s="76" t="inlineStr">
+        <is>
+          <t>Definitions</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B91" s="75" t="inlineStr">
-        <is>
-          <t>Cumulative Payback: Year when cumulative AI revenue first exceeds cumulative AI capex since inception</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="B93" s="77" t="inlineStr">
+        <is>
+          <t>IT Load (GW): Total electrical power consumed by IT equipment (servers, storage, networking)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B92" s="75" t="inlineStr">
-        <is>
-          <t>AI Rev/Capex Ratio: Annual AI revenue divided by annual AI capex; &gt;1.0x means AI revenue exceeds AI investment in that year</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="22" customHeight="1">
-      <c r="A94" s="74" t="inlineStr">
-        <is>
-          <t>Caveats</t>
+      <c r="B94" s="77" t="inlineStr">
+        <is>
+          <t>Power Contracted (GW): Total power capacity secured via PPAs, utility contracts, and on-site generation</t>
         </is>
       </c>
     </row>
@@ -31576,9 +37564,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B95" s="75" t="inlineStr">
-        <is>
-          <t>All neocloud figures are estimates based on limited public disclosure</t>
+      <c r="B95" s="77" t="inlineStr">
+        <is>
+          <t>Power Utilization: IT Load / Power Contracted (higher = more efficient use of secured power)</t>
         </is>
       </c>
     </row>
@@ -31588,9 +37576,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B96" s="75" t="inlineStr">
-        <is>
-          <t>Company-specific DC counts may include leased/colocation facilities</t>
+      <c r="B96" s="77" t="inlineStr">
+        <is>
+          <t>Revenue/MW: Annual revenue ($B) / IT Load (GW); result is in $M/MW (since 1 GW = 1000 MW)</t>
         </is>
       </c>
     </row>
@@ -31600,9 +37588,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B97" s="75" t="inlineStr">
-        <is>
-          <t>Apple revenue is total company revenue (not cloud-specific); DC figures are for internal use</t>
+      <c r="B97" s="77" t="inlineStr">
+        <is>
+          <t>Capex/MW: Annual capex ($B) / IT Load (GW) — investment intensity per MW of IT capacity</t>
         </is>
       </c>
     </row>
@@ -31612,9 +37600,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B98" s="75" t="inlineStr">
-        <is>
-          <t>Meta revenue is total company revenue; DC infrastructure supports ads + AI workloads</t>
+      <c r="B98" s="77" t="inlineStr">
+        <is>
+          <t>Servers (000s): Total server count in thousands across all datacenter locations</t>
         </is>
       </c>
     </row>
@@ -31624,9 +37612,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B99" s="75" t="inlineStr">
-        <is>
-          <t>CyrusOne and QTS are now private; post-acquisition data are estimates</t>
+      <c r="B99" s="77" t="inlineStr">
+        <is>
+          <t>TAM: Total Addressable Market — revenue opportunity for vendors in each supply chain segment</t>
         </is>
       </c>
     </row>
@@ -31636,9 +37624,9 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B100" s="75" t="inlineStr">
-        <is>
-          <t>Forecasts represent base-case scenario; upside/downside cases not included</t>
+      <c r="B100" s="77" t="inlineStr">
+        <is>
+          <t>BOM: Bill of Materials — component and construction cost breakdown per MW of IT load</t>
         </is>
       </c>
     </row>
@@ -31648,25 +37636,153 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B101" s="75" t="inlineStr">
+      <c r="B101" s="77" t="inlineStr">
+        <is>
+          <t>AI Capex: Portion of total capex allocated specifically to AI/ML infrastructure (GPU clusters, AI networking, liquid cooling)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B102" s="77" t="inlineStr">
+        <is>
+          <t>AI Revenue: Revenue directly attributable to AI products and services (cloud AI, GPU-as-a-service, AI tenant leases)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B103" s="77" t="inlineStr">
+        <is>
+          <t>Cumulative Payback: Year when cumulative AI revenue first exceeds cumulative AI capex since inception</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B104" s="77" t="inlineStr">
+        <is>
+          <t>AI Rev/Capex Ratio: Annual AI revenue divided by annual AI capex; &gt;1.0x means AI revenue exceeds AI investment in that year</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="22" customHeight="1">
+      <c r="A106" s="76" t="inlineStr">
+        <is>
+          <t>Caveats</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B107" s="77" t="inlineStr">
+        <is>
+          <t>All neocloud figures are estimates based on limited public disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B108" s="77" t="inlineStr">
+        <is>
+          <t>Company-specific DC counts may include leased/colocation facilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B109" s="77" t="inlineStr">
+        <is>
+          <t>Apple revenue is total company revenue (not cloud-specific); DC figures are for internal use</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B110" s="77" t="inlineStr">
+        <is>
+          <t>Meta revenue is total company revenue; DC infrastructure supports ads + AI workloads</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B111" s="77" t="inlineStr">
+        <is>
+          <t>CyrusOne and QTS are now private; post-acquisition data are estimates</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B112" s="77" t="inlineStr">
+        <is>
+          <t>Forecasts represent base-case scenario; upside/downside cases not included</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B113" s="77" t="inlineStr">
         <is>
           <t>Currency: All figures in USD</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A80:H80"/>
-    <mergeCell ref="A94:H94"/>
+    <mergeCell ref="A62:H62"/>
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A92:H92"/>
+    <mergeCell ref="A106:H106"/>
     <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A73:H73"/>
     <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A72:H72"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A84:H84"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
